--- a/Price and products last2.xlsx
+++ b/Price and products last2.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10810"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11004"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/harshitmittal/Desktop/product_pricing_app/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C65B832D-3055-FA4A-9764-53B9E73778E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{79492FAC-8781-2442-B98A-18453C3ACB64}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="780" windowWidth="36000" windowHeight="22600" firstSheet="1" activeTab="10" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="780" windowWidth="36000" windowHeight="22600" firstSheet="1" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Chain Pulley Block" sheetId="1" r:id="rId1"/>
@@ -647,15 +647,18 @@
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
@@ -841,6 +844,24 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -857,29 +878,11 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1132,10 +1135,10 @@
       </c>
     </row>
     <row r="2" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A2" s="9" t="s">
+      <c r="A2" s="15" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="9" t="s">
+      <c r="B2" s="15" t="s">
         <v>7</v>
       </c>
       <c r="C2" s="1" t="s">
@@ -1152,8 +1155,8 @@
       </c>
     </row>
     <row r="3" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A3" s="10"/>
-      <c r="B3" s="10"/>
+      <c r="A3" s="16"/>
+      <c r="B3" s="16"/>
       <c r="C3" s="1" t="s">
         <v>9</v>
       </c>
@@ -1168,8 +1171,8 @@
       </c>
     </row>
     <row r="4" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A4" s="10"/>
-      <c r="B4" s="10"/>
+      <c r="A4" s="16"/>
+      <c r="B4" s="16"/>
       <c r="C4" s="1" t="s">
         <v>10</v>
       </c>
@@ -1184,8 +1187,8 @@
       </c>
     </row>
     <row r="5" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A5" s="10"/>
-      <c r="B5" s="10"/>
+      <c r="A5" s="16"/>
+      <c r="B5" s="16"/>
       <c r="C5" s="1" t="s">
         <v>11</v>
       </c>
@@ -1200,8 +1203,8 @@
       </c>
     </row>
     <row r="6" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A6" s="10"/>
-      <c r="B6" s="10"/>
+      <c r="A6" s="16"/>
+      <c r="B6" s="16"/>
       <c r="C6" s="1" t="s">
         <v>12</v>
       </c>
@@ -1216,8 +1219,8 @@
       </c>
     </row>
     <row r="7" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A7" s="10"/>
-      <c r="B7" s="11"/>
+      <c r="A7" s="16"/>
+      <c r="B7" s="17"/>
       <c r="C7" s="1" t="s">
         <v>13</v>
       </c>
@@ -1232,8 +1235,8 @@
       </c>
     </row>
     <row r="8" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A8" s="10"/>
-      <c r="B8" s="9" t="s">
+      <c r="A8" s="16"/>
+      <c r="B8" s="15" t="s">
         <v>14</v>
       </c>
       <c r="C8" s="1" t="s">
@@ -1250,8 +1253,8 @@
       </c>
     </row>
     <row r="9" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A9" s="10"/>
-      <c r="B9" s="10"/>
+      <c r="A9" s="16"/>
+      <c r="B9" s="16"/>
       <c r="C9" s="1" t="s">
         <v>15</v>
       </c>
@@ -1266,8 +1269,8 @@
       </c>
     </row>
     <row r="10" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A10" s="10"/>
-      <c r="B10" s="10"/>
+      <c r="A10" s="16"/>
+      <c r="B10" s="16"/>
       <c r="C10" s="1" t="s">
         <v>15</v>
       </c>
@@ -1282,8 +1285,8 @@
       </c>
     </row>
     <row r="11" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A11" s="10"/>
-      <c r="B11" s="10"/>
+      <c r="A11" s="16"/>
+      <c r="B11" s="16"/>
       <c r="C11" s="1" t="s">
         <v>16</v>
       </c>
@@ -1298,8 +1301,8 @@
       </c>
     </row>
     <row r="12" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A12" s="10"/>
-      <c r="B12" s="10"/>
+      <c r="A12" s="16"/>
+      <c r="B12" s="16"/>
       <c r="C12" s="1" t="s">
         <v>16</v>
       </c>
@@ -1314,8 +1317,8 @@
       </c>
     </row>
     <row r="13" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A13" s="10"/>
-      <c r="B13" s="10"/>
+      <c r="A13" s="16"/>
+      <c r="B13" s="16"/>
       <c r="C13" s="1" t="s">
         <v>16</v>
       </c>
@@ -1330,8 +1333,8 @@
       </c>
     </row>
     <row r="14" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A14" s="10"/>
-      <c r="B14" s="10"/>
+      <c r="A14" s="16"/>
+      <c r="B14" s="16"/>
       <c r="C14" s="1" t="s">
         <v>17</v>
       </c>
@@ -1346,8 +1349,8 @@
       </c>
     </row>
     <row r="15" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A15" s="10"/>
-      <c r="B15" s="10"/>
+      <c r="A15" s="16"/>
+      <c r="B15" s="16"/>
       <c r="C15" s="1" t="s">
         <v>17</v>
       </c>
@@ -1362,8 +1365,8 @@
       </c>
     </row>
     <row r="16" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A16" s="10"/>
-      <c r="B16" s="10"/>
+      <c r="A16" s="16"/>
+      <c r="B16" s="16"/>
       <c r="C16" s="1" t="s">
         <v>17</v>
       </c>
@@ -1378,8 +1381,8 @@
       </c>
     </row>
     <row r="17" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A17" s="10"/>
-      <c r="B17" s="11"/>
+      <c r="A17" s="16"/>
+      <c r="B17" s="17"/>
       <c r="C17" s="1" t="s">
         <v>17</v>
       </c>
@@ -1394,8 +1397,8 @@
       </c>
     </row>
     <row r="18" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A18" s="10"/>
-      <c r="B18" s="9" t="s">
+      <c r="A18" s="16"/>
+      <c r="B18" s="15" t="s">
         <v>18</v>
       </c>
       <c r="C18" s="1" t="s">
@@ -1412,8 +1415,8 @@
       </c>
     </row>
     <row r="19" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A19" s="10"/>
-      <c r="B19" s="10"/>
+      <c r="A19" s="16"/>
+      <c r="B19" s="16"/>
       <c r="C19" s="1" t="s">
         <v>19</v>
       </c>
@@ -1428,8 +1431,8 @@
       </c>
     </row>
     <row r="20" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A20" s="10"/>
-      <c r="B20" s="10"/>
+      <c r="A20" s="16"/>
+      <c r="B20" s="16"/>
       <c r="C20" s="1" t="s">
         <v>19</v>
       </c>
@@ -1444,8 +1447,8 @@
       </c>
     </row>
     <row r="21" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A21" s="10"/>
-      <c r="B21" s="10"/>
+      <c r="A21" s="16"/>
+      <c r="B21" s="16"/>
       <c r="C21" s="1" t="s">
         <v>20</v>
       </c>
@@ -1460,8 +1463,8 @@
       </c>
     </row>
     <row r="22" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A22" s="10"/>
-      <c r="B22" s="10"/>
+      <c r="A22" s="16"/>
+      <c r="B22" s="16"/>
       <c r="C22" s="1" t="s">
         <v>20</v>
       </c>
@@ -1476,8 +1479,8 @@
       </c>
     </row>
     <row r="23" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A23" s="10"/>
-      <c r="B23" s="11"/>
+      <c r="A23" s="16"/>
+      <c r="B23" s="17"/>
       <c r="C23" s="1" t="s">
         <v>20</v>
       </c>
@@ -1492,8 +1495,8 @@
       </c>
     </row>
     <row r="24" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A24" s="10"/>
-      <c r="B24" s="9" t="s">
+      <c r="A24" s="16"/>
+      <c r="B24" s="15" t="s">
         <v>21</v>
       </c>
       <c r="C24" s="1" t="s">
@@ -1510,8 +1513,8 @@
       </c>
     </row>
     <row r="25" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A25" s="10"/>
-      <c r="B25" s="10"/>
+      <c r="A25" s="16"/>
+      <c r="B25" s="16"/>
       <c r="C25" s="1" t="s">
         <v>9</v>
       </c>
@@ -1526,8 +1529,8 @@
       </c>
     </row>
     <row r="26" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A26" s="11"/>
-      <c r="B26" s="11"/>
+      <c r="A26" s="17"/>
+      <c r="B26" s="17"/>
       <c r="C26" s="1" t="s">
         <v>10</v>
       </c>
@@ -1570,84 +1573,84 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1" s="17" t="s">
+      <c r="A1" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="17" t="s">
+      <c r="B1" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="17" t="s">
+      <c r="C1" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="17" t="s">
+      <c r="D1" s="9" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="17" t="s">
+      <c r="E1" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="19"/>
+      <c r="F1" s="10"/>
     </row>
     <row r="2" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A2" s="16" t="s">
+      <c r="A2" s="22" t="s">
         <v>188</v>
       </c>
-      <c r="B2" s="20" t="s">
+      <c r="B2" s="24" t="s">
         <v>191</v>
       </c>
-      <c r="C2" s="17" t="s">
+      <c r="C2" s="9" t="s">
         <v>189</v>
       </c>
-      <c r="D2" s="17">
+      <c r="D2" s="9">
         <v>1</v>
       </c>
-      <c r="E2" s="17">
+      <c r="E2" s="9">
         <v>61875</v>
       </c>
-      <c r="F2" s="19"/>
+      <c r="F2" s="10"/>
     </row>
     <row r="3" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A3" s="16"/>
-      <c r="B3" s="21"/>
-      <c r="C3" s="17" t="s">
+      <c r="A3" s="22"/>
+      <c r="B3" s="25"/>
+      <c r="C3" s="9" t="s">
         <v>190</v>
       </c>
-      <c r="D3" s="17">
+      <c r="D3" s="9">
         <v>1.5</v>
       </c>
-      <c r="E3" s="17">
+      <c r="E3" s="9">
         <v>67500</v>
       </c>
-      <c r="F3" s="19"/>
+      <c r="F3" s="10"/>
     </row>
     <row r="4" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A4" s="16"/>
-      <c r="B4" s="22" t="s">
+      <c r="A4" s="22"/>
+      <c r="B4" s="14" t="s">
         <v>192</v>
       </c>
-      <c r="C4" s="23" t="s">
+      <c r="C4" s="11" t="s">
         <v>193</v>
       </c>
-      <c r="D4" s="24">
+      <c r="D4" s="13">
         <v>1</v>
       </c>
-      <c r="E4" s="24">
+      <c r="E4" s="13">
         <v>64375</v>
       </c>
-      <c r="F4" s="19"/>
+      <c r="F4" s="10"/>
     </row>
     <row r="5" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A5" s="16"/>
-      <c r="B5" s="22"/>
-      <c r="C5" s="23" t="s">
+      <c r="A5" s="22"/>
+      <c r="B5" s="14"/>
+      <c r="C5" s="11" t="s">
         <v>194</v>
       </c>
-      <c r="D5" s="23">
+      <c r="D5" s="11">
         <v>1.5</v>
       </c>
-      <c r="E5" s="23">
+      <c r="E5" s="11">
         <v>70000</v>
       </c>
-      <c r="F5" s="19"/>
+      <c r="F5" s="10"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -1674,49 +1677,49 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A1" s="25" t="s">
+      <c r="A1" s="12" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="25" t="s">
+      <c r="B1" s="12" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="25" t="s">
+      <c r="C1" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="25" t="s">
+      <c r="D1" s="12" t="s">
         <v>195</v>
       </c>
-      <c r="E1" s="25" t="s">
+      <c r="E1" s="12" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A2" s="22" t="s">
+      <c r="A2" s="14" t="s">
         <v>196</v>
       </c>
-      <c r="B2" s="22" t="s">
+      <c r="B2" s="14" t="s">
         <v>197</v>
       </c>
-      <c r="C2" s="25" t="s">
+      <c r="C2" s="12" t="s">
         <v>198</v>
       </c>
-      <c r="D2" s="24">
+      <c r="D2" s="13">
         <v>1</v>
       </c>
-      <c r="E2" s="24">
+      <c r="E2" s="13">
         <v>52500</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A3" s="22"/>
-      <c r="B3" s="22"/>
-      <c r="C3" s="25" t="s">
+      <c r="A3" s="14"/>
+      <c r="B3" s="14"/>
+      <c r="C3" s="12" t="s">
         <v>199</v>
       </c>
-      <c r="D3" s="24">
+      <c r="D3" s="13">
         <v>2</v>
       </c>
-      <c r="E3" s="24">
+      <c r="E3" s="13">
         <v>59250</v>
       </c>
     </row>
@@ -1766,10 +1769,10 @@
       </c>
     </row>
     <row r="2" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A2" s="9" t="s">
+      <c r="A2" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="B2" s="9" t="s">
+      <c r="B2" s="15" t="s">
         <v>24</v>
       </c>
       <c r="C2" s="1" t="s">
@@ -1786,8 +1789,8 @@
       </c>
     </row>
     <row r="3" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A3" s="10"/>
-      <c r="B3" s="10"/>
+      <c r="A3" s="16"/>
+      <c r="B3" s="16"/>
       <c r="C3" s="1" t="s">
         <v>26</v>
       </c>
@@ -1802,8 +1805,8 @@
       </c>
     </row>
     <row r="4" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A4" s="10"/>
-      <c r="B4" s="10"/>
+      <c r="A4" s="16"/>
+      <c r="B4" s="16"/>
       <c r="C4" s="1" t="s">
         <v>27</v>
       </c>
@@ -1818,8 +1821,8 @@
       </c>
     </row>
     <row r="5" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A5" s="10"/>
-      <c r="B5" s="10"/>
+      <c r="A5" s="16"/>
+      <c r="B5" s="16"/>
       <c r="C5" s="1" t="s">
         <v>28</v>
       </c>
@@ -1834,8 +1837,8 @@
       </c>
     </row>
     <row r="6" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A6" s="10"/>
-      <c r="B6" s="10"/>
+      <c r="A6" s="16"/>
+      <c r="B6" s="16"/>
       <c r="C6" s="1" t="s">
         <v>29</v>
       </c>
@@ -1850,8 +1853,8 @@
       </c>
     </row>
     <row r="7" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A7" s="10"/>
-      <c r="B7" s="10"/>
+      <c r="A7" s="16"/>
+      <c r="B7" s="16"/>
       <c r="C7" s="1" t="s">
         <v>30</v>
       </c>
@@ -1866,8 +1869,8 @@
       </c>
     </row>
     <row r="8" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A8" s="10"/>
-      <c r="B8" s="11"/>
+      <c r="A8" s="16"/>
+      <c r="B8" s="17"/>
       <c r="C8" s="1" t="s">
         <v>31</v>
       </c>
@@ -1882,8 +1885,8 @@
       </c>
     </row>
     <row r="9" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A9" s="10"/>
-      <c r="B9" s="9" t="s">
+      <c r="A9" s="16"/>
+      <c r="B9" s="15" t="s">
         <v>32</v>
       </c>
       <c r="C9" s="1" t="s">
@@ -1900,8 +1903,8 @@
       </c>
     </row>
     <row r="10" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A10" s="10"/>
-      <c r="B10" s="10"/>
+      <c r="A10" s="16"/>
+      <c r="B10" s="16"/>
       <c r="C10" s="1" t="s">
         <v>26</v>
       </c>
@@ -1916,8 +1919,8 @@
       </c>
     </row>
     <row r="11" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A11" s="10"/>
-      <c r="B11" s="10"/>
+      <c r="A11" s="16"/>
+      <c r="B11" s="16"/>
       <c r="C11" s="1" t="s">
         <v>27</v>
       </c>
@@ -1932,8 +1935,8 @@
       </c>
     </row>
     <row r="12" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A12" s="10"/>
-      <c r="B12" s="10"/>
+      <c r="A12" s="16"/>
+      <c r="B12" s="16"/>
       <c r="C12" s="1" t="s">
         <v>28</v>
       </c>
@@ -1948,8 +1951,8 @@
       </c>
     </row>
     <row r="13" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A13" s="10"/>
-      <c r="B13" s="11"/>
+      <c r="A13" s="16"/>
+      <c r="B13" s="17"/>
       <c r="C13" s="1" t="s">
         <v>29</v>
       </c>
@@ -1964,8 +1967,8 @@
       </c>
     </row>
     <row r="14" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A14" s="10"/>
-      <c r="B14" s="9" t="s">
+      <c r="A14" s="16"/>
+      <c r="B14" s="15" t="s">
         <v>33</v>
       </c>
       <c r="C14" s="1" t="s">
@@ -1980,8 +1983,8 @@
       <c r="F14" s="2"/>
     </row>
     <row r="15" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A15" s="10"/>
-      <c r="B15" s="10"/>
+      <c r="A15" s="16"/>
+      <c r="B15" s="16"/>
       <c r="C15" s="1" t="s">
         <v>35</v>
       </c>
@@ -1994,8 +1997,8 @@
       <c r="F15" s="2"/>
     </row>
     <row r="16" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A16" s="10"/>
-      <c r="B16" s="10"/>
+      <c r="A16" s="16"/>
+      <c r="B16" s="16"/>
       <c r="C16" s="1" t="s">
         <v>36</v>
       </c>
@@ -2008,8 +2011,8 @@
       <c r="F16" s="2"/>
     </row>
     <row r="17" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A17" s="11"/>
-      <c r="B17" s="11"/>
+      <c r="A17" s="17"/>
+      <c r="B17" s="17"/>
       <c r="C17" s="1" t="s">
         <v>37</v>
       </c>
@@ -2064,10 +2067,10 @@
       </c>
     </row>
     <row r="2" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A2" s="9" t="s">
+      <c r="A2" s="15" t="s">
         <v>38</v>
       </c>
-      <c r="B2" s="9" t="s">
+      <c r="B2" s="15" t="s">
         <v>39</v>
       </c>
       <c r="C2" s="1" t="s">
@@ -2081,8 +2084,8 @@
       </c>
     </row>
     <row r="3" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A3" s="10"/>
-      <c r="B3" s="10"/>
+      <c r="A3" s="16"/>
+      <c r="B3" s="16"/>
       <c r="C3" s="1" t="s">
         <v>41</v>
       </c>
@@ -2094,8 +2097,8 @@
       </c>
     </row>
     <row r="4" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A4" s="10"/>
-      <c r="B4" s="11"/>
+      <c r="A4" s="16"/>
+      <c r="B4" s="17"/>
       <c r="C4" s="1" t="s">
         <v>42</v>
       </c>
@@ -2107,8 +2110,8 @@
       </c>
     </row>
     <row r="5" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A5" s="10"/>
-      <c r="B5" s="9" t="s">
+      <c r="A5" s="16"/>
+      <c r="B5" s="15" t="s">
         <v>43</v>
       </c>
       <c r="C5" s="1" t="s">
@@ -2122,8 +2125,8 @@
       </c>
     </row>
     <row r="6" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A6" s="10"/>
-      <c r="B6" s="10"/>
+      <c r="A6" s="16"/>
+      <c r="B6" s="16"/>
       <c r="C6" s="1" t="s">
         <v>45</v>
       </c>
@@ -2135,8 +2138,8 @@
       </c>
     </row>
     <row r="7" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A7" s="10"/>
-      <c r="B7" s="10"/>
+      <c r="A7" s="16"/>
+      <c r="B7" s="16"/>
       <c r="C7" s="1" t="s">
         <v>46</v>
       </c>
@@ -2148,8 +2151,8 @@
       </c>
     </row>
     <row r="8" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A8" s="10"/>
-      <c r="B8" s="10"/>
+      <c r="A8" s="16"/>
+      <c r="B8" s="16"/>
       <c r="C8" s="1" t="s">
         <v>47</v>
       </c>
@@ -2161,8 +2164,8 @@
       </c>
     </row>
     <row r="9" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A9" s="10"/>
-      <c r="B9" s="10"/>
+      <c r="A9" s="16"/>
+      <c r="B9" s="16"/>
       <c r="C9" s="1" t="s">
         <v>48</v>
       </c>
@@ -2174,8 +2177,8 @@
       </c>
     </row>
     <row r="10" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A10" s="10"/>
-      <c r="B10" s="10"/>
+      <c r="A10" s="16"/>
+      <c r="B10" s="16"/>
       <c r="C10" s="1" t="s">
         <v>49</v>
       </c>
@@ -2187,8 +2190,8 @@
       </c>
     </row>
     <row r="11" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A11" s="11"/>
-      <c r="B11" s="11"/>
+      <c r="A11" s="17"/>
+      <c r="B11" s="17"/>
       <c r="C11" s="1" t="s">
         <v>50</v>
       </c>
@@ -2250,10 +2253,10 @@
       </c>
     </row>
     <row r="2" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A2" s="12" t="s">
+      <c r="A2" s="18" t="s">
         <v>38</v>
       </c>
-      <c r="B2" s="9" t="s">
+      <c r="B2" s="15" t="s">
         <v>55</v>
       </c>
       <c r="C2" s="3" t="s">
@@ -2279,8 +2282,8 @@
       </c>
     </row>
     <row r="3" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A3" s="10"/>
-      <c r="B3" s="10"/>
+      <c r="A3" s="16"/>
+      <c r="B3" s="16"/>
       <c r="C3" s="3" t="s">
         <v>58</v>
       </c>
@@ -2304,8 +2307,8 @@
       </c>
     </row>
     <row r="4" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A4" s="10"/>
-      <c r="B4" s="10"/>
+      <c r="A4" s="16"/>
+      <c r="B4" s="16"/>
       <c r="C4" s="3" t="s">
         <v>59</v>
       </c>
@@ -2329,8 +2332,8 @@
       </c>
     </row>
     <row r="5" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A5" s="10"/>
-      <c r="B5" s="10"/>
+      <c r="A5" s="16"/>
+      <c r="B5" s="16"/>
       <c r="C5" s="3" t="s">
         <v>61</v>
       </c>
@@ -2354,8 +2357,8 @@
       </c>
     </row>
     <row r="6" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A6" s="10"/>
-      <c r="B6" s="10"/>
+      <c r="A6" s="16"/>
+      <c r="B6" s="16"/>
       <c r="C6" s="3" t="s">
         <v>62</v>
       </c>
@@ -2379,8 +2382,8 @@
       </c>
     </row>
     <row r="7" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A7" s="10"/>
-      <c r="B7" s="10"/>
+      <c r="A7" s="16"/>
+      <c r="B7" s="16"/>
       <c r="C7" s="3" t="s">
         <v>63</v>
       </c>
@@ -2404,8 +2407,8 @@
       </c>
     </row>
     <row r="8" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A8" s="10"/>
-      <c r="B8" s="10"/>
+      <c r="A8" s="16"/>
+      <c r="B8" s="16"/>
       <c r="C8" s="3" t="s">
         <v>65</v>
       </c>
@@ -2429,8 +2432,8 @@
       </c>
     </row>
     <row r="9" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A9" s="10"/>
-      <c r="B9" s="10"/>
+      <c r="A9" s="16"/>
+      <c r="B9" s="16"/>
       <c r="C9" s="3" t="s">
         <v>66</v>
       </c>
@@ -2454,8 +2457,8 @@
       </c>
     </row>
     <row r="10" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A10" s="10"/>
-      <c r="B10" s="10"/>
+      <c r="A10" s="16"/>
+      <c r="B10" s="16"/>
       <c r="C10" s="3" t="s">
         <v>67</v>
       </c>
@@ -2479,8 +2482,8 @@
       </c>
     </row>
     <row r="11" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A11" s="10"/>
-      <c r="B11" s="10"/>
+      <c r="A11" s="16"/>
+      <c r="B11" s="16"/>
       <c r="C11" s="3" t="s">
         <v>69</v>
       </c>
@@ -2504,8 +2507,8 @@
       </c>
     </row>
     <row r="12" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A12" s="10"/>
-      <c r="B12" s="10"/>
+      <c r="A12" s="16"/>
+      <c r="B12" s="16"/>
       <c r="C12" s="3" t="s">
         <v>71</v>
       </c>
@@ -2529,8 +2532,8 @@
       </c>
     </row>
     <row r="13" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A13" s="10"/>
-      <c r="B13" s="10"/>
+      <c r="A13" s="16"/>
+      <c r="B13" s="16"/>
       <c r="C13" s="3" t="s">
         <v>73</v>
       </c>
@@ -2554,8 +2557,8 @@
       </c>
     </row>
     <row r="14" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A14" s="10"/>
-      <c r="B14" s="10"/>
+      <c r="A14" s="16"/>
+      <c r="B14" s="16"/>
       <c r="C14" s="3" t="s">
         <v>75</v>
       </c>
@@ -2579,8 +2582,8 @@
       </c>
     </row>
     <row r="15" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A15" s="10"/>
-      <c r="B15" s="10"/>
+      <c r="A15" s="16"/>
+      <c r="B15" s="16"/>
       <c r="C15" s="3" t="s">
         <v>76</v>
       </c>
@@ -2604,8 +2607,8 @@
       </c>
     </row>
     <row r="16" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A16" s="10"/>
-      <c r="B16" s="10"/>
+      <c r="A16" s="16"/>
+      <c r="B16" s="16"/>
       <c r="C16" s="3" t="s">
         <v>77</v>
       </c>
@@ -2629,8 +2632,8 @@
       </c>
     </row>
     <row r="17" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A17" s="10"/>
-      <c r="B17" s="10"/>
+      <c r="A17" s="16"/>
+      <c r="B17" s="16"/>
       <c r="C17" s="3" t="s">
         <v>78</v>
       </c>
@@ -2654,8 +2657,8 @@
       </c>
     </row>
     <row r="18" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A18" s="10"/>
-      <c r="B18" s="10"/>
+      <c r="A18" s="16"/>
+      <c r="B18" s="16"/>
       <c r="C18" s="3" t="s">
         <v>79</v>
       </c>
@@ -2679,8 +2682,8 @@
       </c>
     </row>
     <row r="19" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A19" s="10"/>
-      <c r="B19" s="10"/>
+      <c r="A19" s="16"/>
+      <c r="B19" s="16"/>
       <c r="C19" s="3" t="s">
         <v>80</v>
       </c>
@@ -2704,8 +2707,8 @@
       </c>
     </row>
     <row r="20" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A20" s="10"/>
-      <c r="B20" s="10"/>
+      <c r="A20" s="16"/>
+      <c r="B20" s="16"/>
       <c r="C20" s="3" t="s">
         <v>81</v>
       </c>
@@ -2729,8 +2732,8 @@
       </c>
     </row>
     <row r="21" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A21" s="10"/>
-      <c r="B21" s="10"/>
+      <c r="A21" s="16"/>
+      <c r="B21" s="16"/>
       <c r="C21" s="3" t="s">
         <v>82</v>
       </c>
@@ -2754,8 +2757,8 @@
       </c>
     </row>
     <row r="22" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A22" s="10"/>
-      <c r="B22" s="10"/>
+      <c r="A22" s="16"/>
+      <c r="B22" s="16"/>
       <c r="C22" s="3" t="s">
         <v>83</v>
       </c>
@@ -2779,8 +2782,8 @@
       </c>
     </row>
     <row r="23" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A23" s="10"/>
-      <c r="B23" s="10"/>
+      <c r="A23" s="16"/>
+      <c r="B23" s="16"/>
       <c r="C23" s="3" t="s">
         <v>84</v>
       </c>
@@ -2804,8 +2807,8 @@
       </c>
     </row>
     <row r="24" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A24" s="10"/>
-      <c r="B24" s="10"/>
+      <c r="A24" s="16"/>
+      <c r="B24" s="16"/>
       <c r="C24" s="3" t="s">
         <v>85</v>
       </c>
@@ -2829,8 +2832,8 @@
       </c>
     </row>
     <row r="25" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A25" s="10"/>
-      <c r="B25" s="10"/>
+      <c r="A25" s="16"/>
+      <c r="B25" s="16"/>
       <c r="C25" s="3" t="s">
         <v>86</v>
       </c>
@@ -2854,8 +2857,8 @@
       </c>
     </row>
     <row r="26" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A26" s="10"/>
-      <c r="B26" s="10"/>
+      <c r="A26" s="16"/>
+      <c r="B26" s="16"/>
       <c r="C26" s="3" t="s">
         <v>87</v>
       </c>
@@ -2879,8 +2882,8 @@
       </c>
     </row>
     <row r="27" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A27" s="10"/>
-      <c r="B27" s="10"/>
+      <c r="A27" s="16"/>
+      <c r="B27" s="16"/>
       <c r="C27" s="3" t="s">
         <v>88</v>
       </c>
@@ -2904,8 +2907,8 @@
       </c>
     </row>
     <row r="28" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A28" s="10"/>
-      <c r="B28" s="10"/>
+      <c r="A28" s="16"/>
+      <c r="B28" s="16"/>
       <c r="C28" s="3" t="s">
         <v>89</v>
       </c>
@@ -2929,8 +2932,8 @@
       </c>
     </row>
     <row r="29" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A29" s="10"/>
-      <c r="B29" s="10"/>
+      <c r="A29" s="16"/>
+      <c r="B29" s="16"/>
       <c r="C29" s="3" t="s">
         <v>90</v>
       </c>
@@ -2954,8 +2957,8 @@
       </c>
     </row>
     <row r="30" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A30" s="10"/>
-      <c r="B30" s="10"/>
+      <c r="A30" s="16"/>
+      <c r="B30" s="16"/>
       <c r="C30" s="3" t="s">
         <v>91</v>
       </c>
@@ -2979,8 +2982,8 @@
       </c>
     </row>
     <row r="31" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A31" s="10"/>
-      <c r="B31" s="10"/>
+      <c r="A31" s="16"/>
+      <c r="B31" s="16"/>
       <c r="C31" s="3" t="s">
         <v>92</v>
       </c>
@@ -3004,8 +3007,8 @@
       </c>
     </row>
     <row r="32" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A32" s="10"/>
-      <c r="B32" s="10"/>
+      <c r="A32" s="16"/>
+      <c r="B32" s="16"/>
       <c r="C32" s="3" t="s">
         <v>93</v>
       </c>
@@ -3029,8 +3032,8 @@
       </c>
     </row>
     <row r="33" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A33" s="10"/>
-      <c r="B33" s="10"/>
+      <c r="A33" s="16"/>
+      <c r="B33" s="16"/>
       <c r="C33" s="3" t="s">
         <v>94</v>
       </c>
@@ -3054,8 +3057,8 @@
       </c>
     </row>
     <row r="34" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A34" s="10"/>
-      <c r="B34" s="10"/>
+      <c r="A34" s="16"/>
+      <c r="B34" s="16"/>
       <c r="C34" s="3" t="s">
         <v>95</v>
       </c>
@@ -3079,8 +3082,8 @@
       </c>
     </row>
     <row r="35" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A35" s="11"/>
-      <c r="B35" s="11"/>
+      <c r="A35" s="17"/>
+      <c r="B35" s="17"/>
       <c r="C35" s="1" t="s">
         <v>97</v>
       </c>
@@ -3133,39 +3136,39 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="15" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="9" t="s">
+      <c r="B1" s="15" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="9" t="s">
+      <c r="C1" s="15" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="9" t="s">
+      <c r="D1" s="15" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="9" t="s">
+      <c r="E1" s="15" t="s">
         <v>99</v>
       </c>
-      <c r="F1" s="13" t="s">
+      <c r="F1" s="19" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="14"/>
-      <c r="H1" s="14"/>
-      <c r="I1" s="14"/>
-      <c r="J1" s="14"/>
-      <c r="K1" s="15"/>
+      <c r="G1" s="20"/>
+      <c r="H1" s="20"/>
+      <c r="I1" s="20"/>
+      <c r="J1" s="20"/>
+      <c r="K1" s="21"/>
       <c r="L1" s="5"/>
       <c r="M1" s="5"/>
       <c r="N1" s="5"/>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A2" s="11"/>
-      <c r="B2" s="11"/>
-      <c r="C2" s="11"/>
-      <c r="D2" s="11"/>
-      <c r="E2" s="11"/>
+      <c r="A2" s="17"/>
+      <c r="B2" s="17"/>
+      <c r="C2" s="17"/>
+      <c r="D2" s="17"/>
+      <c r="E2" s="17"/>
       <c r="F2" s="1" t="s">
         <v>100</v>
       </c>
@@ -3189,10 +3192,10 @@
       <c r="N2" s="5"/>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A3" s="9" t="s">
+      <c r="A3" s="15" t="s">
         <v>104</v>
       </c>
-      <c r="B3" s="9" t="s">
+      <c r="B3" s="15" t="s">
         <v>105</v>
       </c>
       <c r="C3" s="1" t="s">
@@ -3227,8 +3230,8 @@
       <c r="N3" s="6"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A4" s="10"/>
-      <c r="B4" s="10"/>
+      <c r="A4" s="16"/>
+      <c r="B4" s="16"/>
       <c r="C4" s="1" t="s">
         <v>107</v>
       </c>
@@ -3261,8 +3264,8 @@
       <c r="N4" s="6"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A5" s="10"/>
-      <c r="B5" s="10"/>
+      <c r="A5" s="16"/>
+      <c r="B5" s="16"/>
       <c r="C5" s="1" t="s">
         <v>108</v>
       </c>
@@ -3295,8 +3298,8 @@
       <c r="N5" s="6"/>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A6" s="11"/>
-      <c r="B6" s="11"/>
+      <c r="A6" s="17"/>
+      <c r="B6" s="17"/>
       <c r="C6" s="1" t="s">
         <v>109</v>
       </c>
@@ -3363,39 +3366,39 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="15" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="9" t="s">
+      <c r="B1" s="15" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="9" t="s">
+      <c r="C1" s="15" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="9" t="s">
+      <c r="D1" s="15" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="9" t="s">
+      <c r="E1" s="15" t="s">
         <v>99</v>
       </c>
-      <c r="F1" s="13" t="s">
+      <c r="F1" s="19" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="14"/>
-      <c r="H1" s="14"/>
-      <c r="I1" s="14"/>
-      <c r="J1" s="14"/>
-      <c r="K1" s="14"/>
-      <c r="L1" s="14"/>
-      <c r="M1" s="14"/>
-      <c r="N1" s="15"/>
+      <c r="G1" s="20"/>
+      <c r="H1" s="20"/>
+      <c r="I1" s="20"/>
+      <c r="J1" s="20"/>
+      <c r="K1" s="20"/>
+      <c r="L1" s="20"/>
+      <c r="M1" s="20"/>
+      <c r="N1" s="21"/>
     </row>
     <row r="2" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A2" s="11"/>
-      <c r="B2" s="11"/>
-      <c r="C2" s="11"/>
-      <c r="D2" s="11"/>
-      <c r="E2" s="11"/>
+      <c r="A2" s="17"/>
+      <c r="B2" s="17"/>
+      <c r="C2" s="17"/>
+      <c r="D2" s="17"/>
+      <c r="E2" s="17"/>
       <c r="F2" s="1" t="s">
         <v>100</v>
       </c>
@@ -3425,10 +3428,10 @@
       </c>
     </row>
     <row r="3" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A3" s="12" t="s">
+      <c r="A3" s="18" t="s">
         <v>104</v>
       </c>
-      <c r="B3" s="9" t="s">
+      <c r="B3" s="15" t="s">
         <v>115</v>
       </c>
       <c r="C3" s="2" t="s">
@@ -3463,8 +3466,8 @@
       </c>
     </row>
     <row r="4" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A4" s="10"/>
-      <c r="B4" s="10"/>
+      <c r="A4" s="16"/>
+      <c r="B4" s="16"/>
       <c r="C4" s="2" t="s">
         <v>117</v>
       </c>
@@ -3503,8 +3506,8 @@
       </c>
     </row>
     <row r="5" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A5" s="10"/>
-      <c r="B5" s="10"/>
+      <c r="A5" s="16"/>
+      <c r="B5" s="16"/>
       <c r="C5" s="2" t="s">
         <v>118</v>
       </c>
@@ -3543,8 +3546,8 @@
       </c>
     </row>
     <row r="6" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A6" s="10"/>
-      <c r="B6" s="10"/>
+      <c r="A6" s="16"/>
+      <c r="B6" s="16"/>
       <c r="C6" s="2" t="s">
         <v>119</v>
       </c>
@@ -3583,8 +3586,8 @@
       </c>
     </row>
     <row r="7" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A7" s="10"/>
-      <c r="B7" s="10"/>
+      <c r="A7" s="16"/>
+      <c r="B7" s="16"/>
       <c r="C7" s="2" t="s">
         <v>120</v>
       </c>
@@ -3619,8 +3622,8 @@
       </c>
     </row>
     <row r="8" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A8" s="10"/>
-      <c r="B8" s="10"/>
+      <c r="A8" s="16"/>
+      <c r="B8" s="16"/>
       <c r="C8" s="2" t="s">
         <v>121</v>
       </c>
@@ -3655,8 +3658,8 @@
       </c>
     </row>
     <row r="9" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A9" s="10"/>
-      <c r="B9" s="10"/>
+      <c r="A9" s="16"/>
+      <c r="B9" s="16"/>
       <c r="C9" s="2" t="s">
         <v>122</v>
       </c>
@@ -3691,8 +3694,8 @@
       </c>
     </row>
     <row r="10" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A10" s="10"/>
-      <c r="B10" s="10"/>
+      <c r="A10" s="16"/>
+      <c r="B10" s="16"/>
       <c r="C10" s="2" t="s">
         <v>124</v>
       </c>
@@ -3731,8 +3734,8 @@
       </c>
     </row>
     <row r="11" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A11" s="10"/>
-      <c r="B11" s="10"/>
+      <c r="A11" s="16"/>
+      <c r="B11" s="16"/>
       <c r="C11" s="2" t="s">
         <v>125</v>
       </c>
@@ -3771,8 +3774,8 @@
       </c>
     </row>
     <row r="12" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A12" s="10"/>
-      <c r="B12" s="10"/>
+      <c r="A12" s="16"/>
+      <c r="B12" s="16"/>
       <c r="C12" s="2" t="s">
         <v>126</v>
       </c>
@@ -3811,8 +3814,8 @@
       </c>
     </row>
     <row r="13" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A13" s="10"/>
-      <c r="B13" s="10"/>
+      <c r="A13" s="16"/>
+      <c r="B13" s="16"/>
       <c r="C13" s="2" t="s">
         <v>127</v>
       </c>
@@ -3851,8 +3854,8 @@
       </c>
     </row>
     <row r="14" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A14" s="10"/>
-      <c r="B14" s="10"/>
+      <c r="A14" s="16"/>
+      <c r="B14" s="16"/>
       <c r="C14" s="2" t="s">
         <v>128</v>
       </c>
@@ -3891,8 +3894,8 @@
       </c>
     </row>
     <row r="15" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A15" s="10"/>
-      <c r="B15" s="10"/>
+      <c r="A15" s="16"/>
+      <c r="B15" s="16"/>
       <c r="C15" s="2" t="s">
         <v>129</v>
       </c>
@@ -3931,8 +3934,8 @@
       </c>
     </row>
     <row r="16" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A16" s="10"/>
-      <c r="B16" s="10"/>
+      <c r="A16" s="16"/>
+      <c r="B16" s="16"/>
       <c r="C16" s="2" t="s">
         <v>130</v>
       </c>
@@ -3971,8 +3974,8 @@
       </c>
     </row>
     <row r="17" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A17" s="10"/>
-      <c r="B17" s="10"/>
+      <c r="A17" s="16"/>
+      <c r="B17" s="16"/>
       <c r="C17" s="2" t="s">
         <v>131</v>
       </c>
@@ -4011,8 +4014,8 @@
       </c>
     </row>
     <row r="18" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A18" s="10"/>
-      <c r="B18" s="10"/>
+      <c r="A18" s="16"/>
+      <c r="B18" s="16"/>
       <c r="C18" s="2" t="s">
         <v>132</v>
       </c>
@@ -4051,8 +4054,8 @@
       </c>
     </row>
     <row r="19" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A19" s="10"/>
-      <c r="B19" s="10"/>
+      <c r="A19" s="16"/>
+      <c r="B19" s="16"/>
       <c r="C19" s="2" t="s">
         <v>133</v>
       </c>
@@ -4091,8 +4094,8 @@
       </c>
     </row>
     <row r="20" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A20" s="10"/>
-      <c r="B20" s="10"/>
+      <c r="A20" s="16"/>
+      <c r="B20" s="16"/>
       <c r="C20" s="2" t="s">
         <v>134</v>
       </c>
@@ -4131,8 +4134,8 @@
       </c>
     </row>
     <row r="21" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A21" s="10"/>
-      <c r="B21" s="10"/>
+      <c r="A21" s="16"/>
+      <c r="B21" s="16"/>
       <c r="C21" s="2" t="s">
         <v>135</v>
       </c>
@@ -4171,8 +4174,8 @@
       </c>
     </row>
     <row r="22" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A22" s="10"/>
-      <c r="B22" s="10"/>
+      <c r="A22" s="16"/>
+      <c r="B22" s="16"/>
       <c r="C22" s="2" t="s">
         <v>136</v>
       </c>
@@ -4211,8 +4214,8 @@
       </c>
     </row>
     <row r="23" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A23" s="10"/>
-      <c r="B23" s="10"/>
+      <c r="A23" s="16"/>
+      <c r="B23" s="16"/>
       <c r="C23" s="2" t="s">
         <v>137</v>
       </c>
@@ -4251,8 +4254,8 @@
       </c>
     </row>
     <row r="24" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A24" s="10"/>
-      <c r="B24" s="10"/>
+      <c r="A24" s="16"/>
+      <c r="B24" s="16"/>
       <c r="C24" s="2" t="s">
         <v>138</v>
       </c>
@@ -4291,8 +4294,8 @@
       </c>
     </row>
     <row r="25" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A25" s="10"/>
-      <c r="B25" s="10"/>
+      <c r="A25" s="16"/>
+      <c r="B25" s="16"/>
       <c r="C25" s="2" t="s">
         <v>139</v>
       </c>
@@ -4331,8 +4334,8 @@
       </c>
     </row>
     <row r="26" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A26" s="10"/>
-      <c r="B26" s="10"/>
+      <c r="A26" s="16"/>
+      <c r="B26" s="16"/>
       <c r="C26" s="2" t="s">
         <v>140</v>
       </c>
@@ -4371,8 +4374,8 @@
       </c>
     </row>
     <row r="27" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A27" s="10"/>
-      <c r="B27" s="10"/>
+      <c r="A27" s="16"/>
+      <c r="B27" s="16"/>
       <c r="C27" s="2" t="s">
         <v>141</v>
       </c>
@@ -4411,8 +4414,8 @@
       </c>
     </row>
     <row r="28" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A28" s="10"/>
-      <c r="B28" s="10"/>
+      <c r="A28" s="16"/>
+      <c r="B28" s="16"/>
       <c r="C28" s="2" t="s">
         <v>142</v>
       </c>
@@ -4451,8 +4454,8 @@
       </c>
     </row>
     <row r="29" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A29" s="10"/>
-      <c r="B29" s="10"/>
+      <c r="A29" s="16"/>
+      <c r="B29" s="16"/>
       <c r="C29" s="2" t="s">
         <v>143</v>
       </c>
@@ -4491,8 +4494,8 @@
       </c>
     </row>
     <row r="30" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A30" s="10"/>
-      <c r="B30" s="10"/>
+      <c r="A30" s="16"/>
+      <c r="B30" s="16"/>
       <c r="C30" s="2" t="s">
         <v>144</v>
       </c>
@@ -4531,8 +4534,8 @@
       </c>
     </row>
     <row r="31" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A31" s="10"/>
-      <c r="B31" s="10"/>
+      <c r="A31" s="16"/>
+      <c r="B31" s="16"/>
       <c r="C31" s="2" t="s">
         <v>145</v>
       </c>
@@ -4571,8 +4574,8 @@
       </c>
     </row>
     <row r="32" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A32" s="10"/>
-      <c r="B32" s="10"/>
+      <c r="A32" s="16"/>
+      <c r="B32" s="16"/>
       <c r="C32" s="2" t="s">
         <v>146</v>
       </c>
@@ -4611,8 +4614,8 @@
       </c>
     </row>
     <row r="33" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A33" s="11"/>
-      <c r="B33" s="11"/>
+      <c r="A33" s="17"/>
+      <c r="B33" s="17"/>
       <c r="C33" s="2" t="s">
         <v>147</v>
       </c>
@@ -4652,6 +4655,7 @@
     </row>
   </sheetData>
   <mergeCells count="8">
+    <mergeCell ref="F1:N1"/>
     <mergeCell ref="A3:A33"/>
     <mergeCell ref="B3:B33"/>
     <mergeCell ref="E1:E2"/>
@@ -4659,7 +4663,6 @@
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
     <mergeCell ref="D1:D2"/>
-    <mergeCell ref="F1:N1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -4683,32 +4686,32 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="15" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="9" t="s">
+      <c r="B1" s="15" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="9" t="s">
+      <c r="C1" s="15" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="9" t="s">
+      <c r="D1" s="15" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="9" t="s">
+      <c r="E1" s="15" t="s">
         <v>148</v>
       </c>
-      <c r="F1" s="13" t="s">
+      <c r="F1" s="19" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="15"/>
+      <c r="G1" s="21"/>
     </row>
     <row r="2" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A2" s="11"/>
-      <c r="B2" s="11"/>
-      <c r="C2" s="11"/>
-      <c r="D2" s="11"/>
-      <c r="E2" s="11"/>
+      <c r="A2" s="17"/>
+      <c r="B2" s="17"/>
+      <c r="C2" s="17"/>
+      <c r="D2" s="17"/>
+      <c r="E2" s="17"/>
       <c r="F2" s="1" t="s">
         <v>149</v>
       </c>
@@ -4717,7 +4720,7 @@
       </c>
     </row>
     <row r="3" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A3" s="9" t="s">
+      <c r="A3" s="15" t="s">
         <v>151</v>
       </c>
       <c r="B3" s="1" t="s">
@@ -4740,7 +4743,7 @@
       </c>
     </row>
     <row r="4" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A4" s="10"/>
+      <c r="A4" s="16"/>
       <c r="B4" s="1" t="s">
         <v>152</v>
       </c>
@@ -4761,7 +4764,7 @@
       </c>
     </row>
     <row r="5" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A5" s="10"/>
+      <c r="A5" s="16"/>
       <c r="B5" s="1" t="s">
         <v>152</v>
       </c>
@@ -4782,7 +4785,7 @@
       </c>
     </row>
     <row r="6" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A6" s="10"/>
+      <c r="A6" s="16"/>
       <c r="B6" s="1" t="s">
         <v>152</v>
       </c>
@@ -4803,7 +4806,7 @@
       </c>
     </row>
     <row r="7" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A7" s="10"/>
+      <c r="A7" s="16"/>
       <c r="B7" s="1" t="s">
         <v>152</v>
       </c>
@@ -4824,7 +4827,7 @@
       </c>
     </row>
     <row r="8" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A8" s="10"/>
+      <c r="A8" s="16"/>
       <c r="B8" s="1" t="s">
         <v>152</v>
       </c>
@@ -4845,7 +4848,7 @@
       </c>
     </row>
     <row r="9" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A9" s="10"/>
+      <c r="A9" s="16"/>
       <c r="B9" s="1" t="s">
         <v>152</v>
       </c>
@@ -4866,7 +4869,7 @@
       </c>
     </row>
     <row r="10" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A10" s="10"/>
+      <c r="A10" s="16"/>
       <c r="B10" s="1" t="s">
         <v>160</v>
       </c>
@@ -4887,7 +4890,7 @@
       </c>
     </row>
     <row r="11" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A11" s="10"/>
+      <c r="A11" s="16"/>
       <c r="B11" s="1" t="s">
         <v>160</v>
       </c>
@@ -4908,7 +4911,7 @@
       </c>
     </row>
     <row r="12" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A12" s="10"/>
+      <c r="A12" s="16"/>
       <c r="B12" s="1" t="s">
         <v>160</v>
       </c>
@@ -4929,7 +4932,7 @@
       </c>
     </row>
     <row r="13" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A13" s="10"/>
+      <c r="A13" s="16"/>
       <c r="B13" s="1" t="s">
         <v>160</v>
       </c>
@@ -4950,7 +4953,7 @@
       </c>
     </row>
     <row r="14" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A14" s="10"/>
+      <c r="A14" s="16"/>
       <c r="B14" s="1" t="s">
         <v>160</v>
       </c>
@@ -4971,7 +4974,7 @@
       </c>
     </row>
     <row r="15" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A15" s="11"/>
+      <c r="A15" s="17"/>
       <c r="B15" s="1" t="s">
         <v>160</v>
       </c>
@@ -5042,10 +5045,10 @@
       </c>
     </row>
     <row r="2" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A2" s="9" t="s">
+      <c r="A2" s="15" t="s">
         <v>168</v>
       </c>
-      <c r="B2" s="9" t="s">
+      <c r="B2" s="15" t="s">
         <v>169</v>
       </c>
       <c r="C2" s="1" t="s">
@@ -5062,8 +5065,8 @@
       </c>
     </row>
     <row r="3" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A3" s="10"/>
-      <c r="B3" s="10"/>
+      <c r="A3" s="16"/>
+      <c r="B3" s="16"/>
       <c r="C3" s="1" t="s">
         <v>171</v>
       </c>
@@ -5078,8 +5081,8 @@
       </c>
     </row>
     <row r="4" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A4" s="10"/>
-      <c r="B4" s="10"/>
+      <c r="A4" s="16"/>
+      <c r="B4" s="16"/>
       <c r="C4" s="1" t="s">
         <v>172</v>
       </c>
@@ -5094,8 +5097,8 @@
       </c>
     </row>
     <row r="5" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A5" s="10"/>
-      <c r="B5" s="10"/>
+      <c r="A5" s="16"/>
+      <c r="B5" s="16"/>
       <c r="C5" s="1" t="s">
         <v>173</v>
       </c>
@@ -5110,8 +5113,8 @@
       </c>
     </row>
     <row r="6" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A6" s="10"/>
-      <c r="B6" s="10"/>
+      <c r="A6" s="16"/>
+      <c r="B6" s="16"/>
       <c r="C6" s="1" t="s">
         <v>174</v>
       </c>
@@ -5126,8 +5129,8 @@
       </c>
     </row>
     <row r="7" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A7" s="10"/>
-      <c r="B7" s="10"/>
+      <c r="A7" s="16"/>
+      <c r="B7" s="16"/>
       <c r="C7" s="1" t="s">
         <v>175</v>
       </c>
@@ -5142,8 +5145,8 @@
       </c>
     </row>
     <row r="8" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A8" s="10"/>
-      <c r="B8" s="10"/>
+      <c r="A8" s="16"/>
+      <c r="B8" s="16"/>
       <c r="C8" s="1" t="s">
         <v>176</v>
       </c>
@@ -5158,8 +5161,8 @@
       </c>
     </row>
     <row r="9" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A9" s="10"/>
-      <c r="B9" s="10"/>
+      <c r="A9" s="16"/>
+      <c r="B9" s="16"/>
       <c r="C9" s="1" t="s">
         <v>177</v>
       </c>
@@ -5174,8 +5177,8 @@
       </c>
     </row>
     <row r="10" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A10" s="10"/>
-      <c r="B10" s="10"/>
+      <c r="A10" s="16"/>
+      <c r="B10" s="16"/>
       <c r="C10" s="1" t="s">
         <v>178</v>
       </c>
@@ -5190,8 +5193,8 @@
       </c>
     </row>
     <row r="11" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A11" s="10"/>
-      <c r="B11" s="10"/>
+      <c r="A11" s="16"/>
+      <c r="B11" s="16"/>
       <c r="C11" s="1" t="s">
         <v>179</v>
       </c>
@@ -5206,8 +5209,8 @@
       </c>
     </row>
     <row r="12" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A12" s="11"/>
-      <c r="B12" s="11"/>
+      <c r="A12" s="17"/>
+      <c r="B12" s="17"/>
       <c r="C12" s="1" t="s">
         <v>180</v>
       </c>
@@ -5268,71 +5271,71 @@
       </c>
     </row>
     <row r="2" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A2" s="16" t="s">
+      <c r="A2" s="22" t="s">
         <v>182</v>
       </c>
-      <c r="B2" s="16" t="s">
+      <c r="B2" s="22" t="s">
         <v>183</v>
       </c>
-      <c r="C2" s="17" t="s">
+      <c r="C2" s="9" t="s">
         <v>184</v>
       </c>
-      <c r="D2" s="17">
+      <c r="D2" s="9">
         <v>1.5</v>
       </c>
-      <c r="E2" s="17">
+      <c r="E2" s="9">
         <v>550</v>
       </c>
-      <c r="F2" s="17">
-        <v>13200</v>
+      <c r="F2" s="9">
+        <v>14500</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A3" s="18"/>
-      <c r="B3" s="18"/>
-      <c r="C3" s="17" t="s">
+      <c r="A3" s="23"/>
+      <c r="B3" s="23"/>
+      <c r="C3" s="9" t="s">
         <v>185</v>
       </c>
-      <c r="D3" s="17">
+      <c r="D3" s="9">
         <v>1.5</v>
       </c>
-      <c r="E3" s="17">
+      <c r="E3" s="9">
         <v>685</v>
       </c>
-      <c r="F3" s="17">
-        <v>13800</v>
+      <c r="F3" s="9">
+        <v>15000</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A4" s="18"/>
-      <c r="B4" s="18"/>
-      <c r="C4" s="17" t="s">
+      <c r="A4" s="23"/>
+      <c r="B4" s="23"/>
+      <c r="C4" s="9" t="s">
         <v>186</v>
       </c>
-      <c r="D4" s="17">
+      <c r="D4" s="9">
         <v>2.5</v>
       </c>
-      <c r="E4" s="17">
+      <c r="E4" s="9">
         <v>550</v>
       </c>
-      <c r="F4" s="17">
-        <v>14000</v>
+      <c r="F4" s="9">
+        <v>15500</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A5" s="18"/>
-      <c r="B5" s="18"/>
-      <c r="C5" s="17" t="s">
+      <c r="A5" s="23"/>
+      <c r="B5" s="23"/>
+      <c r="C5" s="9" t="s">
         <v>187</v>
       </c>
-      <c r="D5" s="17">
+      <c r="D5" s="9">
         <v>2.5</v>
       </c>
-      <c r="E5" s="17">
+      <c r="E5" s="9">
         <v>685</v>
       </c>
-      <c r="F5" s="17">
-        <v>14600</v>
+      <c r="F5" s="9">
+        <v>16000</v>
       </c>
     </row>
   </sheetData>

--- a/Price and products last2.xlsx
+++ b/Price and products last2.xlsx
@@ -859,9 +859,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -875,14 +876,13 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1135,10 +1135,10 @@
       </c>
     </row>
     <row r="2" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A2" s="15" t="s">
+      <c r="A2" s="16" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="15" t="s">
+      <c r="B2" s="16" t="s">
         <v>7</v>
       </c>
       <c r="C2" s="1" t="s">
@@ -1155,8 +1155,8 @@
       </c>
     </row>
     <row r="3" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A3" s="16"/>
-      <c r="B3" s="16"/>
+      <c r="A3" s="17"/>
+      <c r="B3" s="17"/>
       <c r="C3" s="1" t="s">
         <v>9</v>
       </c>
@@ -1171,8 +1171,8 @@
       </c>
     </row>
     <row r="4" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A4" s="16"/>
-      <c r="B4" s="16"/>
+      <c r="A4" s="17"/>
+      <c r="B4" s="17"/>
       <c r="C4" s="1" t="s">
         <v>10</v>
       </c>
@@ -1187,8 +1187,8 @@
       </c>
     </row>
     <row r="5" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A5" s="16"/>
-      <c r="B5" s="16"/>
+      <c r="A5" s="17"/>
+      <c r="B5" s="17"/>
       <c r="C5" s="1" t="s">
         <v>11</v>
       </c>
@@ -1203,8 +1203,8 @@
       </c>
     </row>
     <row r="6" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A6" s="16"/>
-      <c r="B6" s="16"/>
+      <c r="A6" s="17"/>
+      <c r="B6" s="17"/>
       <c r="C6" s="1" t="s">
         <v>12</v>
       </c>
@@ -1219,8 +1219,8 @@
       </c>
     </row>
     <row r="7" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A7" s="16"/>
-      <c r="B7" s="17"/>
+      <c r="A7" s="17"/>
+      <c r="B7" s="18"/>
       <c r="C7" s="1" t="s">
         <v>13</v>
       </c>
@@ -1235,8 +1235,8 @@
       </c>
     </row>
     <row r="8" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A8" s="16"/>
-      <c r="B8" s="15" t="s">
+      <c r="A8" s="17"/>
+      <c r="B8" s="16" t="s">
         <v>14</v>
       </c>
       <c r="C8" s="1" t="s">
@@ -1253,8 +1253,8 @@
       </c>
     </row>
     <row r="9" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A9" s="16"/>
-      <c r="B9" s="16"/>
+      <c r="A9" s="17"/>
+      <c r="B9" s="17"/>
       <c r="C9" s="1" t="s">
         <v>15</v>
       </c>
@@ -1269,8 +1269,8 @@
       </c>
     </row>
     <row r="10" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A10" s="16"/>
-      <c r="B10" s="16"/>
+      <c r="A10" s="17"/>
+      <c r="B10" s="17"/>
       <c r="C10" s="1" t="s">
         <v>15</v>
       </c>
@@ -1285,8 +1285,8 @@
       </c>
     </row>
     <row r="11" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A11" s="16"/>
-      <c r="B11" s="16"/>
+      <c r="A11" s="17"/>
+      <c r="B11" s="17"/>
       <c r="C11" s="1" t="s">
         <v>16</v>
       </c>
@@ -1301,8 +1301,8 @@
       </c>
     </row>
     <row r="12" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A12" s="16"/>
-      <c r="B12" s="16"/>
+      <c r="A12" s="17"/>
+      <c r="B12" s="17"/>
       <c r="C12" s="1" t="s">
         <v>16</v>
       </c>
@@ -1317,8 +1317,8 @@
       </c>
     </row>
     <row r="13" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A13" s="16"/>
-      <c r="B13" s="16"/>
+      <c r="A13" s="17"/>
+      <c r="B13" s="17"/>
       <c r="C13" s="1" t="s">
         <v>16</v>
       </c>
@@ -1333,8 +1333,8 @@
       </c>
     </row>
     <row r="14" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A14" s="16"/>
-      <c r="B14" s="16"/>
+      <c r="A14" s="17"/>
+      <c r="B14" s="17"/>
       <c r="C14" s="1" t="s">
         <v>17</v>
       </c>
@@ -1349,8 +1349,8 @@
       </c>
     </row>
     <row r="15" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A15" s="16"/>
-      <c r="B15" s="16"/>
+      <c r="A15" s="17"/>
+      <c r="B15" s="17"/>
       <c r="C15" s="1" t="s">
         <v>17</v>
       </c>
@@ -1365,8 +1365,8 @@
       </c>
     </row>
     <row r="16" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A16" s="16"/>
-      <c r="B16" s="16"/>
+      <c r="A16" s="17"/>
+      <c r="B16" s="17"/>
       <c r="C16" s="1" t="s">
         <v>17</v>
       </c>
@@ -1381,8 +1381,8 @@
       </c>
     </row>
     <row r="17" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A17" s="16"/>
-      <c r="B17" s="17"/>
+      <c r="A17" s="17"/>
+      <c r="B17" s="18"/>
       <c r="C17" s="1" t="s">
         <v>17</v>
       </c>
@@ -1397,8 +1397,8 @@
       </c>
     </row>
     <row r="18" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A18" s="16"/>
-      <c r="B18" s="15" t="s">
+      <c r="A18" s="17"/>
+      <c r="B18" s="16" t="s">
         <v>18</v>
       </c>
       <c r="C18" s="1" t="s">
@@ -1415,8 +1415,8 @@
       </c>
     </row>
     <row r="19" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A19" s="16"/>
-      <c r="B19" s="16"/>
+      <c r="A19" s="17"/>
+      <c r="B19" s="17"/>
       <c r="C19" s="1" t="s">
         <v>19</v>
       </c>
@@ -1431,8 +1431,8 @@
       </c>
     </row>
     <row r="20" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A20" s="16"/>
-      <c r="B20" s="16"/>
+      <c r="A20" s="17"/>
+      <c r="B20" s="17"/>
       <c r="C20" s="1" t="s">
         <v>19</v>
       </c>
@@ -1447,8 +1447,8 @@
       </c>
     </row>
     <row r="21" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A21" s="16"/>
-      <c r="B21" s="16"/>
+      <c r="A21" s="17"/>
+      <c r="B21" s="17"/>
       <c r="C21" s="1" t="s">
         <v>20</v>
       </c>
@@ -1463,8 +1463,8 @@
       </c>
     </row>
     <row r="22" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A22" s="16"/>
-      <c r="B22" s="16"/>
+      <c r="A22" s="17"/>
+      <c r="B22" s="17"/>
       <c r="C22" s="1" t="s">
         <v>20</v>
       </c>
@@ -1479,8 +1479,8 @@
       </c>
     </row>
     <row r="23" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A23" s="16"/>
-      <c r="B23" s="17"/>
+      <c r="A23" s="17"/>
+      <c r="B23" s="18"/>
       <c r="C23" s="1" t="s">
         <v>20</v>
       </c>
@@ -1495,8 +1495,8 @@
       </c>
     </row>
     <row r="24" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A24" s="16"/>
-      <c r="B24" s="15" t="s">
+      <c r="A24" s="17"/>
+      <c r="B24" s="16" t="s">
         <v>21</v>
       </c>
       <c r="C24" s="1" t="s">
@@ -1513,8 +1513,8 @@
       </c>
     </row>
     <row r="25" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A25" s="16"/>
-      <c r="B25" s="16"/>
+      <c r="A25" s="17"/>
+      <c r="B25" s="17"/>
       <c r="C25" s="1" t="s">
         <v>9</v>
       </c>
@@ -1529,8 +1529,8 @@
       </c>
     </row>
     <row r="26" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A26" s="17"/>
-      <c r="B26" s="17"/>
+      <c r="A26" s="18"/>
+      <c r="B26" s="18"/>
       <c r="C26" s="1" t="s">
         <v>10</v>
       </c>
@@ -1591,10 +1591,10 @@
       <c r="F1" s="10"/>
     </row>
     <row r="2" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A2" s="22" t="s">
+      <c r="A2" s="14" t="s">
         <v>188</v>
       </c>
-      <c r="B2" s="24" t="s">
+      <c r="B2" s="23" t="s">
         <v>191</v>
       </c>
       <c r="C2" s="9" t="s">
@@ -1609,8 +1609,8 @@
       <c r="F2" s="10"/>
     </row>
     <row r="3" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A3" s="22"/>
-      <c r="B3" s="25"/>
+      <c r="A3" s="14"/>
+      <c r="B3" s="24"/>
       <c r="C3" s="9" t="s">
         <v>190</v>
       </c>
@@ -1623,8 +1623,8 @@
       <c r="F3" s="10"/>
     </row>
     <row r="4" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A4" s="22"/>
-      <c r="B4" s="14" t="s">
+      <c r="A4" s="14"/>
+      <c r="B4" s="25" t="s">
         <v>192</v>
       </c>
       <c r="C4" s="11" t="s">
@@ -1639,8 +1639,8 @@
       <c r="F4" s="10"/>
     </row>
     <row r="5" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A5" s="22"/>
-      <c r="B5" s="14"/>
+      <c r="A5" s="14"/>
+      <c r="B5" s="25"/>
       <c r="C5" s="11" t="s">
         <v>194</v>
       </c>
@@ -1694,10 +1694,10 @@
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A2" s="14" t="s">
+      <c r="A2" s="25" t="s">
         <v>196</v>
       </c>
-      <c r="B2" s="14" t="s">
+      <c r="B2" s="25" t="s">
         <v>197</v>
       </c>
       <c r="C2" s="12" t="s">
@@ -1711,8 +1711,8 @@
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A3" s="14"/>
-      <c r="B3" s="14"/>
+      <c r="A3" s="25"/>
+      <c r="B3" s="25"/>
       <c r="C3" s="12" t="s">
         <v>199</v>
       </c>
@@ -1769,10 +1769,10 @@
       </c>
     </row>
     <row r="2" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A2" s="15" t="s">
+      <c r="A2" s="16" t="s">
         <v>23</v>
       </c>
-      <c r="B2" s="15" t="s">
+      <c r="B2" s="16" t="s">
         <v>24</v>
       </c>
       <c r="C2" s="1" t="s">
@@ -1789,8 +1789,8 @@
       </c>
     </row>
     <row r="3" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A3" s="16"/>
-      <c r="B3" s="16"/>
+      <c r="A3" s="17"/>
+      <c r="B3" s="17"/>
       <c r="C3" s="1" t="s">
         <v>26</v>
       </c>
@@ -1805,8 +1805,8 @@
       </c>
     </row>
     <row r="4" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A4" s="16"/>
-      <c r="B4" s="16"/>
+      <c r="A4" s="17"/>
+      <c r="B4" s="17"/>
       <c r="C4" s="1" t="s">
         <v>27</v>
       </c>
@@ -1821,8 +1821,8 @@
       </c>
     </row>
     <row r="5" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A5" s="16"/>
-      <c r="B5" s="16"/>
+      <c r="A5" s="17"/>
+      <c r="B5" s="17"/>
       <c r="C5" s="1" t="s">
         <v>28</v>
       </c>
@@ -1837,8 +1837,8 @@
       </c>
     </row>
     <row r="6" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A6" s="16"/>
-      <c r="B6" s="16"/>
+      <c r="A6" s="17"/>
+      <c r="B6" s="17"/>
       <c r="C6" s="1" t="s">
         <v>29</v>
       </c>
@@ -1853,8 +1853,8 @@
       </c>
     </row>
     <row r="7" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A7" s="16"/>
-      <c r="B7" s="16"/>
+      <c r="A7" s="17"/>
+      <c r="B7" s="17"/>
       <c r="C7" s="1" t="s">
         <v>30</v>
       </c>
@@ -1869,8 +1869,8 @@
       </c>
     </row>
     <row r="8" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A8" s="16"/>
-      <c r="B8" s="17"/>
+      <c r="A8" s="17"/>
+      <c r="B8" s="18"/>
       <c r="C8" s="1" t="s">
         <v>31</v>
       </c>
@@ -1885,8 +1885,8 @@
       </c>
     </row>
     <row r="9" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A9" s="16"/>
-      <c r="B9" s="15" t="s">
+      <c r="A9" s="17"/>
+      <c r="B9" s="16" t="s">
         <v>32</v>
       </c>
       <c r="C9" s="1" t="s">
@@ -1903,8 +1903,8 @@
       </c>
     </row>
     <row r="10" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A10" s="16"/>
-      <c r="B10" s="16"/>
+      <c r="A10" s="17"/>
+      <c r="B10" s="17"/>
       <c r="C10" s="1" t="s">
         <v>26</v>
       </c>
@@ -1919,8 +1919,8 @@
       </c>
     </row>
     <row r="11" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A11" s="16"/>
-      <c r="B11" s="16"/>
+      <c r="A11" s="17"/>
+      <c r="B11" s="17"/>
       <c r="C11" s="1" t="s">
         <v>27</v>
       </c>
@@ -1935,8 +1935,8 @@
       </c>
     </row>
     <row r="12" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A12" s="16"/>
-      <c r="B12" s="16"/>
+      <c r="A12" s="17"/>
+      <c r="B12" s="17"/>
       <c r="C12" s="1" t="s">
         <v>28</v>
       </c>
@@ -1951,8 +1951,8 @@
       </c>
     </row>
     <row r="13" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A13" s="16"/>
-      <c r="B13" s="17"/>
+      <c r="A13" s="17"/>
+      <c r="B13" s="18"/>
       <c r="C13" s="1" t="s">
         <v>29</v>
       </c>
@@ -1967,8 +1967,8 @@
       </c>
     </row>
     <row r="14" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A14" s="16"/>
-      <c r="B14" s="15" t="s">
+      <c r="A14" s="17"/>
+      <c r="B14" s="16" t="s">
         <v>33</v>
       </c>
       <c r="C14" s="1" t="s">
@@ -1983,8 +1983,8 @@
       <c r="F14" s="2"/>
     </row>
     <row r="15" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A15" s="16"/>
-      <c r="B15" s="16"/>
+      <c r="A15" s="17"/>
+      <c r="B15" s="17"/>
       <c r="C15" s="1" t="s">
         <v>35</v>
       </c>
@@ -1997,8 +1997,8 @@
       <c r="F15" s="2"/>
     </row>
     <row r="16" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A16" s="16"/>
-      <c r="B16" s="16"/>
+      <c r="A16" s="17"/>
+      <c r="B16" s="17"/>
       <c r="C16" s="1" t="s">
         <v>36</v>
       </c>
@@ -2011,8 +2011,8 @@
       <c r="F16" s="2"/>
     </row>
     <row r="17" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A17" s="17"/>
-      <c r="B17" s="17"/>
+      <c r="A17" s="18"/>
+      <c r="B17" s="18"/>
       <c r="C17" s="1" t="s">
         <v>37</v>
       </c>
@@ -2067,10 +2067,10 @@
       </c>
     </row>
     <row r="2" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A2" s="15" t="s">
+      <c r="A2" s="16" t="s">
         <v>38</v>
       </c>
-      <c r="B2" s="15" t="s">
+      <c r="B2" s="16" t="s">
         <v>39</v>
       </c>
       <c r="C2" s="1" t="s">
@@ -2084,8 +2084,8 @@
       </c>
     </row>
     <row r="3" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A3" s="16"/>
-      <c r="B3" s="16"/>
+      <c r="A3" s="17"/>
+      <c r="B3" s="17"/>
       <c r="C3" s="1" t="s">
         <v>41</v>
       </c>
@@ -2097,8 +2097,8 @@
       </c>
     </row>
     <row r="4" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A4" s="16"/>
-      <c r="B4" s="17"/>
+      <c r="A4" s="17"/>
+      <c r="B4" s="18"/>
       <c r="C4" s="1" t="s">
         <v>42</v>
       </c>
@@ -2110,8 +2110,8 @@
       </c>
     </row>
     <row r="5" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A5" s="16"/>
-      <c r="B5" s="15" t="s">
+      <c r="A5" s="17"/>
+      <c r="B5" s="16" t="s">
         <v>43</v>
       </c>
       <c r="C5" s="1" t="s">
@@ -2125,8 +2125,8 @@
       </c>
     </row>
     <row r="6" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A6" s="16"/>
-      <c r="B6" s="16"/>
+      <c r="A6" s="17"/>
+      <c r="B6" s="17"/>
       <c r="C6" s="1" t="s">
         <v>45</v>
       </c>
@@ -2138,8 +2138,8 @@
       </c>
     </row>
     <row r="7" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A7" s="16"/>
-      <c r="B7" s="16"/>
+      <c r="A7" s="17"/>
+      <c r="B7" s="17"/>
       <c r="C7" s="1" t="s">
         <v>46</v>
       </c>
@@ -2151,8 +2151,8 @@
       </c>
     </row>
     <row r="8" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A8" s="16"/>
-      <c r="B8" s="16"/>
+      <c r="A8" s="17"/>
+      <c r="B8" s="17"/>
       <c r="C8" s="1" t="s">
         <v>47</v>
       </c>
@@ -2164,8 +2164,8 @@
       </c>
     </row>
     <row r="9" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A9" s="16"/>
-      <c r="B9" s="16"/>
+      <c r="A9" s="17"/>
+      <c r="B9" s="17"/>
       <c r="C9" s="1" t="s">
         <v>48</v>
       </c>
@@ -2177,8 +2177,8 @@
       </c>
     </row>
     <row r="10" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A10" s="16"/>
-      <c r="B10" s="16"/>
+      <c r="A10" s="17"/>
+      <c r="B10" s="17"/>
       <c r="C10" s="1" t="s">
         <v>49</v>
       </c>
@@ -2190,8 +2190,8 @@
       </c>
     </row>
     <row r="11" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A11" s="17"/>
-      <c r="B11" s="17"/>
+      <c r="A11" s="18"/>
+      <c r="B11" s="18"/>
       <c r="C11" s="1" t="s">
         <v>50</v>
       </c>
@@ -2253,10 +2253,10 @@
       </c>
     </row>
     <row r="2" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A2" s="18" t="s">
+      <c r="A2" s="19" t="s">
         <v>38</v>
       </c>
-      <c r="B2" s="15" t="s">
+      <c r="B2" s="16" t="s">
         <v>55</v>
       </c>
       <c r="C2" s="3" t="s">
@@ -2282,8 +2282,8 @@
       </c>
     </row>
     <row r="3" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A3" s="16"/>
-      <c r="B3" s="16"/>
+      <c r="A3" s="17"/>
+      <c r="B3" s="17"/>
       <c r="C3" s="3" t="s">
         <v>58</v>
       </c>
@@ -2307,8 +2307,8 @@
       </c>
     </row>
     <row r="4" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A4" s="16"/>
-      <c r="B4" s="16"/>
+      <c r="A4" s="17"/>
+      <c r="B4" s="17"/>
       <c r="C4" s="3" t="s">
         <v>59</v>
       </c>
@@ -2332,8 +2332,8 @@
       </c>
     </row>
     <row r="5" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A5" s="16"/>
-      <c r="B5" s="16"/>
+      <c r="A5" s="17"/>
+      <c r="B5" s="17"/>
       <c r="C5" s="3" t="s">
         <v>61</v>
       </c>
@@ -2357,8 +2357,8 @@
       </c>
     </row>
     <row r="6" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A6" s="16"/>
-      <c r="B6" s="16"/>
+      <c r="A6" s="17"/>
+      <c r="B6" s="17"/>
       <c r="C6" s="3" t="s">
         <v>62</v>
       </c>
@@ -2382,8 +2382,8 @@
       </c>
     </row>
     <row r="7" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A7" s="16"/>
-      <c r="B7" s="16"/>
+      <c r="A7" s="17"/>
+      <c r="B7" s="17"/>
       <c r="C7" s="3" t="s">
         <v>63</v>
       </c>
@@ -2407,8 +2407,8 @@
       </c>
     </row>
     <row r="8" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A8" s="16"/>
-      <c r="B8" s="16"/>
+      <c r="A8" s="17"/>
+      <c r="B8" s="17"/>
       <c r="C8" s="3" t="s">
         <v>65</v>
       </c>
@@ -2432,8 +2432,8 @@
       </c>
     </row>
     <row r="9" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A9" s="16"/>
-      <c r="B9" s="16"/>
+      <c r="A9" s="17"/>
+      <c r="B9" s="17"/>
       <c r="C9" s="3" t="s">
         <v>66</v>
       </c>
@@ -2457,8 +2457,8 @@
       </c>
     </row>
     <row r="10" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A10" s="16"/>
-      <c r="B10" s="16"/>
+      <c r="A10" s="17"/>
+      <c r="B10" s="17"/>
       <c r="C10" s="3" t="s">
         <v>67</v>
       </c>
@@ -2482,8 +2482,8 @@
       </c>
     </row>
     <row r="11" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A11" s="16"/>
-      <c r="B11" s="16"/>
+      <c r="A11" s="17"/>
+      <c r="B11" s="17"/>
       <c r="C11" s="3" t="s">
         <v>69</v>
       </c>
@@ -2507,8 +2507,8 @@
       </c>
     </row>
     <row r="12" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A12" s="16"/>
-      <c r="B12" s="16"/>
+      <c r="A12" s="17"/>
+      <c r="B12" s="17"/>
       <c r="C12" s="3" t="s">
         <v>71</v>
       </c>
@@ -2532,8 +2532,8 @@
       </c>
     </row>
     <row r="13" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A13" s="16"/>
-      <c r="B13" s="16"/>
+      <c r="A13" s="17"/>
+      <c r="B13" s="17"/>
       <c r="C13" s="3" t="s">
         <v>73</v>
       </c>
@@ -2557,8 +2557,8 @@
       </c>
     </row>
     <row r="14" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A14" s="16"/>
-      <c r="B14" s="16"/>
+      <c r="A14" s="17"/>
+      <c r="B14" s="17"/>
       <c r="C14" s="3" t="s">
         <v>75</v>
       </c>
@@ -2582,8 +2582,8 @@
       </c>
     </row>
     <row r="15" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A15" s="16"/>
-      <c r="B15" s="16"/>
+      <c r="A15" s="17"/>
+      <c r="B15" s="17"/>
       <c r="C15" s="3" t="s">
         <v>76</v>
       </c>
@@ -2607,8 +2607,8 @@
       </c>
     </row>
     <row r="16" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A16" s="16"/>
-      <c r="B16" s="16"/>
+      <c r="A16" s="17"/>
+      <c r="B16" s="17"/>
       <c r="C16" s="3" t="s">
         <v>77</v>
       </c>
@@ -2632,8 +2632,8 @@
       </c>
     </row>
     <row r="17" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A17" s="16"/>
-      <c r="B17" s="16"/>
+      <c r="A17" s="17"/>
+      <c r="B17" s="17"/>
       <c r="C17" s="3" t="s">
         <v>78</v>
       </c>
@@ -2657,8 +2657,8 @@
       </c>
     </row>
     <row r="18" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A18" s="16"/>
-      <c r="B18" s="16"/>
+      <c r="A18" s="17"/>
+      <c r="B18" s="17"/>
       <c r="C18" s="3" t="s">
         <v>79</v>
       </c>
@@ -2682,8 +2682,8 @@
       </c>
     </row>
     <row r="19" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A19" s="16"/>
-      <c r="B19" s="16"/>
+      <c r="A19" s="17"/>
+      <c r="B19" s="17"/>
       <c r="C19" s="3" t="s">
         <v>80</v>
       </c>
@@ -2707,8 +2707,8 @@
       </c>
     </row>
     <row r="20" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A20" s="16"/>
-      <c r="B20" s="16"/>
+      <c r="A20" s="17"/>
+      <c r="B20" s="17"/>
       <c r="C20" s="3" t="s">
         <v>81</v>
       </c>
@@ -2732,8 +2732,8 @@
       </c>
     </row>
     <row r="21" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A21" s="16"/>
-      <c r="B21" s="16"/>
+      <c r="A21" s="17"/>
+      <c r="B21" s="17"/>
       <c r="C21" s="3" t="s">
         <v>82</v>
       </c>
@@ -2757,8 +2757,8 @@
       </c>
     </row>
     <row r="22" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A22" s="16"/>
-      <c r="B22" s="16"/>
+      <c r="A22" s="17"/>
+      <c r="B22" s="17"/>
       <c r="C22" s="3" t="s">
         <v>83</v>
       </c>
@@ -2782,8 +2782,8 @@
       </c>
     </row>
     <row r="23" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A23" s="16"/>
-      <c r="B23" s="16"/>
+      <c r="A23" s="17"/>
+      <c r="B23" s="17"/>
       <c r="C23" s="3" t="s">
         <v>84</v>
       </c>
@@ -2807,8 +2807,8 @@
       </c>
     </row>
     <row r="24" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A24" s="16"/>
-      <c r="B24" s="16"/>
+      <c r="A24" s="17"/>
+      <c r="B24" s="17"/>
       <c r="C24" s="3" t="s">
         <v>85</v>
       </c>
@@ -2832,8 +2832,8 @@
       </c>
     </row>
     <row r="25" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A25" s="16"/>
-      <c r="B25" s="16"/>
+      <c r="A25" s="17"/>
+      <c r="B25" s="17"/>
       <c r="C25" s="3" t="s">
         <v>86</v>
       </c>
@@ -2857,8 +2857,8 @@
       </c>
     </row>
     <row r="26" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A26" s="16"/>
-      <c r="B26" s="16"/>
+      <c r="A26" s="17"/>
+      <c r="B26" s="17"/>
       <c r="C26" s="3" t="s">
         <v>87</v>
       </c>
@@ -2882,8 +2882,8 @@
       </c>
     </row>
     <row r="27" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A27" s="16"/>
-      <c r="B27" s="16"/>
+      <c r="A27" s="17"/>
+      <c r="B27" s="17"/>
       <c r="C27" s="3" t="s">
         <v>88</v>
       </c>
@@ -2907,8 +2907,8 @@
       </c>
     </row>
     <row r="28" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A28" s="16"/>
-      <c r="B28" s="16"/>
+      <c r="A28" s="17"/>
+      <c r="B28" s="17"/>
       <c r="C28" s="3" t="s">
         <v>89</v>
       </c>
@@ -2932,8 +2932,8 @@
       </c>
     </row>
     <row r="29" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A29" s="16"/>
-      <c r="B29" s="16"/>
+      <c r="A29" s="17"/>
+      <c r="B29" s="17"/>
       <c r="C29" s="3" t="s">
         <v>90</v>
       </c>
@@ -2957,8 +2957,8 @@
       </c>
     </row>
     <row r="30" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A30" s="16"/>
-      <c r="B30" s="16"/>
+      <c r="A30" s="17"/>
+      <c r="B30" s="17"/>
       <c r="C30" s="3" t="s">
         <v>91</v>
       </c>
@@ -2982,8 +2982,8 @@
       </c>
     </row>
     <row r="31" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A31" s="16"/>
-      <c r="B31" s="16"/>
+      <c r="A31" s="17"/>
+      <c r="B31" s="17"/>
       <c r="C31" s="3" t="s">
         <v>92</v>
       </c>
@@ -3007,8 +3007,8 @@
       </c>
     </row>
     <row r="32" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A32" s="16"/>
-      <c r="B32" s="16"/>
+      <c r="A32" s="17"/>
+      <c r="B32" s="17"/>
       <c r="C32" s="3" t="s">
         <v>93</v>
       </c>
@@ -3032,8 +3032,8 @@
       </c>
     </row>
     <row r="33" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A33" s="16"/>
-      <c r="B33" s="16"/>
+      <c r="A33" s="17"/>
+      <c r="B33" s="17"/>
       <c r="C33" s="3" t="s">
         <v>94</v>
       </c>
@@ -3057,8 +3057,8 @@
       </c>
     </row>
     <row r="34" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A34" s="16"/>
-      <c r="B34" s="16"/>
+      <c r="A34" s="17"/>
+      <c r="B34" s="17"/>
       <c r="C34" s="3" t="s">
         <v>95</v>
       </c>
@@ -3082,8 +3082,8 @@
       </c>
     </row>
     <row r="35" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A35" s="17"/>
-      <c r="B35" s="17"/>
+      <c r="A35" s="18"/>
+      <c r="B35" s="18"/>
       <c r="C35" s="1" t="s">
         <v>97</v>
       </c>
@@ -3136,39 +3136,39 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A1" s="15" t="s">
+      <c r="A1" s="16" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="15" t="s">
+      <c r="B1" s="16" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="15" t="s">
+      <c r="C1" s="16" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="15" t="s">
+      <c r="D1" s="16" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="15" t="s">
+      <c r="E1" s="16" t="s">
         <v>99</v>
       </c>
-      <c r="F1" s="19" t="s">
+      <c r="F1" s="20" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="20"/>
-      <c r="H1" s="20"/>
-      <c r="I1" s="20"/>
-      <c r="J1" s="20"/>
-      <c r="K1" s="21"/>
+      <c r="G1" s="21"/>
+      <c r="H1" s="21"/>
+      <c r="I1" s="21"/>
+      <c r="J1" s="21"/>
+      <c r="K1" s="22"/>
       <c r="L1" s="5"/>
       <c r="M1" s="5"/>
       <c r="N1" s="5"/>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A2" s="17"/>
-      <c r="B2" s="17"/>
-      <c r="C2" s="17"/>
-      <c r="D2" s="17"/>
-      <c r="E2" s="17"/>
+      <c r="A2" s="18"/>
+      <c r="B2" s="18"/>
+      <c r="C2" s="18"/>
+      <c r="D2" s="18"/>
+      <c r="E2" s="18"/>
       <c r="F2" s="1" t="s">
         <v>100</v>
       </c>
@@ -3192,10 +3192,10 @@
       <c r="N2" s="5"/>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A3" s="15" t="s">
+      <c r="A3" s="16" t="s">
         <v>104</v>
       </c>
-      <c r="B3" s="15" t="s">
+      <c r="B3" s="16" t="s">
         <v>105</v>
       </c>
       <c r="C3" s="1" t="s">
@@ -3230,8 +3230,8 @@
       <c r="N3" s="6"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A4" s="16"/>
-      <c r="B4" s="16"/>
+      <c r="A4" s="17"/>
+      <c r="B4" s="17"/>
       <c r="C4" s="1" t="s">
         <v>107</v>
       </c>
@@ -3264,8 +3264,8 @@
       <c r="N4" s="6"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A5" s="16"/>
-      <c r="B5" s="16"/>
+      <c r="A5" s="17"/>
+      <c r="B5" s="17"/>
       <c r="C5" s="1" t="s">
         <v>108</v>
       </c>
@@ -3298,8 +3298,8 @@
       <c r="N5" s="6"/>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A6" s="17"/>
-      <c r="B6" s="17"/>
+      <c r="A6" s="18"/>
+      <c r="B6" s="18"/>
       <c r="C6" s="1" t="s">
         <v>109</v>
       </c>
@@ -3366,39 +3366,39 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1" s="15" t="s">
+      <c r="A1" s="16" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="15" t="s">
+      <c r="B1" s="16" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="15" t="s">
+      <c r="C1" s="16" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="15" t="s">
+      <c r="D1" s="16" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="15" t="s">
+      <c r="E1" s="16" t="s">
         <v>99</v>
       </c>
-      <c r="F1" s="19" t="s">
+      <c r="F1" s="20" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="20"/>
-      <c r="H1" s="20"/>
-      <c r="I1" s="20"/>
-      <c r="J1" s="20"/>
-      <c r="K1" s="20"/>
-      <c r="L1" s="20"/>
-      <c r="M1" s="20"/>
-      <c r="N1" s="21"/>
+      <c r="G1" s="21"/>
+      <c r="H1" s="21"/>
+      <c r="I1" s="21"/>
+      <c r="J1" s="21"/>
+      <c r="K1" s="21"/>
+      <c r="L1" s="21"/>
+      <c r="M1" s="21"/>
+      <c r="N1" s="22"/>
     </row>
     <row r="2" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A2" s="17"/>
-      <c r="B2" s="17"/>
-      <c r="C2" s="17"/>
-      <c r="D2" s="17"/>
-      <c r="E2" s="17"/>
+      <c r="A2" s="18"/>
+      <c r="B2" s="18"/>
+      <c r="C2" s="18"/>
+      <c r="D2" s="18"/>
+      <c r="E2" s="18"/>
       <c r="F2" s="1" t="s">
         <v>100</v>
       </c>
@@ -3428,10 +3428,10 @@
       </c>
     </row>
     <row r="3" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A3" s="18" t="s">
+      <c r="A3" s="19" t="s">
         <v>104</v>
       </c>
-      <c r="B3" s="15" t="s">
+      <c r="B3" s="16" t="s">
         <v>115</v>
       </c>
       <c r="C3" s="2" t="s">
@@ -3466,8 +3466,8 @@
       </c>
     </row>
     <row r="4" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A4" s="16"/>
-      <c r="B4" s="16"/>
+      <c r="A4" s="17"/>
+      <c r="B4" s="17"/>
       <c r="C4" s="2" t="s">
         <v>117</v>
       </c>
@@ -3506,8 +3506,8 @@
       </c>
     </row>
     <row r="5" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A5" s="16"/>
-      <c r="B5" s="16"/>
+      <c r="A5" s="17"/>
+      <c r="B5" s="17"/>
       <c r="C5" s="2" t="s">
         <v>118</v>
       </c>
@@ -3546,8 +3546,8 @@
       </c>
     </row>
     <row r="6" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A6" s="16"/>
-      <c r="B6" s="16"/>
+      <c r="A6" s="17"/>
+      <c r="B6" s="17"/>
       <c r="C6" s="2" t="s">
         <v>119</v>
       </c>
@@ -3586,8 +3586,8 @@
       </c>
     </row>
     <row r="7" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A7" s="16"/>
-      <c r="B7" s="16"/>
+      <c r="A7" s="17"/>
+      <c r="B7" s="17"/>
       <c r="C7" s="2" t="s">
         <v>120</v>
       </c>
@@ -3622,8 +3622,8 @@
       </c>
     </row>
     <row r="8" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A8" s="16"/>
-      <c r="B8" s="16"/>
+      <c r="A8" s="17"/>
+      <c r="B8" s="17"/>
       <c r="C8" s="2" t="s">
         <v>121</v>
       </c>
@@ -3658,8 +3658,8 @@
       </c>
     </row>
     <row r="9" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A9" s="16"/>
-      <c r="B9" s="16"/>
+      <c r="A9" s="17"/>
+      <c r="B9" s="17"/>
       <c r="C9" s="2" t="s">
         <v>122</v>
       </c>
@@ -3694,8 +3694,8 @@
       </c>
     </row>
     <row r="10" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A10" s="16"/>
-      <c r="B10" s="16"/>
+      <c r="A10" s="17"/>
+      <c r="B10" s="17"/>
       <c r="C10" s="2" t="s">
         <v>124</v>
       </c>
@@ -3734,8 +3734,8 @@
       </c>
     </row>
     <row r="11" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A11" s="16"/>
-      <c r="B11" s="16"/>
+      <c r="A11" s="17"/>
+      <c r="B11" s="17"/>
       <c r="C11" s="2" t="s">
         <v>125</v>
       </c>
@@ -3774,8 +3774,8 @@
       </c>
     </row>
     <row r="12" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A12" s="16"/>
-      <c r="B12" s="16"/>
+      <c r="A12" s="17"/>
+      <c r="B12" s="17"/>
       <c r="C12" s="2" t="s">
         <v>126</v>
       </c>
@@ -3814,8 +3814,8 @@
       </c>
     </row>
     <row r="13" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A13" s="16"/>
-      <c r="B13" s="16"/>
+      <c r="A13" s="17"/>
+      <c r="B13" s="17"/>
       <c r="C13" s="2" t="s">
         <v>127</v>
       </c>
@@ -3854,8 +3854,8 @@
       </c>
     </row>
     <row r="14" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A14" s="16"/>
-      <c r="B14" s="16"/>
+      <c r="A14" s="17"/>
+      <c r="B14" s="17"/>
       <c r="C14" s="2" t="s">
         <v>128</v>
       </c>
@@ -3894,8 +3894,8 @@
       </c>
     </row>
     <row r="15" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A15" s="16"/>
-      <c r="B15" s="16"/>
+      <c r="A15" s="17"/>
+      <c r="B15" s="17"/>
       <c r="C15" s="2" t="s">
         <v>129</v>
       </c>
@@ -3934,8 +3934,8 @@
       </c>
     </row>
     <row r="16" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A16" s="16"/>
-      <c r="B16" s="16"/>
+      <c r="A16" s="17"/>
+      <c r="B16" s="17"/>
       <c r="C16" s="2" t="s">
         <v>130</v>
       </c>
@@ -3974,8 +3974,8 @@
       </c>
     </row>
     <row r="17" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A17" s="16"/>
-      <c r="B17" s="16"/>
+      <c r="A17" s="17"/>
+      <c r="B17" s="17"/>
       <c r="C17" s="2" t="s">
         <v>131</v>
       </c>
@@ -4014,8 +4014,8 @@
       </c>
     </row>
     <row r="18" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A18" s="16"/>
-      <c r="B18" s="16"/>
+      <c r="A18" s="17"/>
+      <c r="B18" s="17"/>
       <c r="C18" s="2" t="s">
         <v>132</v>
       </c>
@@ -4054,8 +4054,8 @@
       </c>
     </row>
     <row r="19" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A19" s="16"/>
-      <c r="B19" s="16"/>
+      <c r="A19" s="17"/>
+      <c r="B19" s="17"/>
       <c r="C19" s="2" t="s">
         <v>133</v>
       </c>
@@ -4094,8 +4094,8 @@
       </c>
     </row>
     <row r="20" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A20" s="16"/>
-      <c r="B20" s="16"/>
+      <c r="A20" s="17"/>
+      <c r="B20" s="17"/>
       <c r="C20" s="2" t="s">
         <v>134</v>
       </c>
@@ -4134,8 +4134,8 @@
       </c>
     </row>
     <row r="21" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A21" s="16"/>
-      <c r="B21" s="16"/>
+      <c r="A21" s="17"/>
+      <c r="B21" s="17"/>
       <c r="C21" s="2" t="s">
         <v>135</v>
       </c>
@@ -4174,8 +4174,8 @@
       </c>
     </row>
     <row r="22" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A22" s="16"/>
-      <c r="B22" s="16"/>
+      <c r="A22" s="17"/>
+      <c r="B22" s="17"/>
       <c r="C22" s="2" t="s">
         <v>136</v>
       </c>
@@ -4214,8 +4214,8 @@
       </c>
     </row>
     <row r="23" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A23" s="16"/>
-      <c r="B23" s="16"/>
+      <c r="A23" s="17"/>
+      <c r="B23" s="17"/>
       <c r="C23" s="2" t="s">
         <v>137</v>
       </c>
@@ -4254,8 +4254,8 @@
       </c>
     </row>
     <row r="24" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A24" s="16"/>
-      <c r="B24" s="16"/>
+      <c r="A24" s="17"/>
+      <c r="B24" s="17"/>
       <c r="C24" s="2" t="s">
         <v>138</v>
       </c>
@@ -4294,8 +4294,8 @@
       </c>
     </row>
     <row r="25" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A25" s="16"/>
-      <c r="B25" s="16"/>
+      <c r="A25" s="17"/>
+      <c r="B25" s="17"/>
       <c r="C25" s="2" t="s">
         <v>139</v>
       </c>
@@ -4334,8 +4334,8 @@
       </c>
     </row>
     <row r="26" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A26" s="16"/>
-      <c r="B26" s="16"/>
+      <c r="A26" s="17"/>
+      <c r="B26" s="17"/>
       <c r="C26" s="2" t="s">
         <v>140</v>
       </c>
@@ -4374,8 +4374,8 @@
       </c>
     </row>
     <row r="27" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A27" s="16"/>
-      <c r="B27" s="16"/>
+      <c r="A27" s="17"/>
+      <c r="B27" s="17"/>
       <c r="C27" s="2" t="s">
         <v>141</v>
       </c>
@@ -4414,8 +4414,8 @@
       </c>
     </row>
     <row r="28" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A28" s="16"/>
-      <c r="B28" s="16"/>
+      <c r="A28" s="17"/>
+      <c r="B28" s="17"/>
       <c r="C28" s="2" t="s">
         <v>142</v>
       </c>
@@ -4454,8 +4454,8 @@
       </c>
     </row>
     <row r="29" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A29" s="16"/>
-      <c r="B29" s="16"/>
+      <c r="A29" s="17"/>
+      <c r="B29" s="17"/>
       <c r="C29" s="2" t="s">
         <v>143</v>
       </c>
@@ -4494,8 +4494,8 @@
       </c>
     </row>
     <row r="30" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A30" s="16"/>
-      <c r="B30" s="16"/>
+      <c r="A30" s="17"/>
+      <c r="B30" s="17"/>
       <c r="C30" s="2" t="s">
         <v>144</v>
       </c>
@@ -4534,8 +4534,8 @@
       </c>
     </row>
     <row r="31" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A31" s="16"/>
-      <c r="B31" s="16"/>
+      <c r="A31" s="17"/>
+      <c r="B31" s="17"/>
       <c r="C31" s="2" t="s">
         <v>145</v>
       </c>
@@ -4574,8 +4574,8 @@
       </c>
     </row>
     <row r="32" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A32" s="16"/>
-      <c r="B32" s="16"/>
+      <c r="A32" s="17"/>
+      <c r="B32" s="17"/>
       <c r="C32" s="2" t="s">
         <v>146</v>
       </c>
@@ -4614,8 +4614,8 @@
       </c>
     </row>
     <row r="33" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A33" s="17"/>
-      <c r="B33" s="17"/>
+      <c r="A33" s="18"/>
+      <c r="B33" s="18"/>
       <c r="C33" s="2" t="s">
         <v>147</v>
       </c>
@@ -4686,32 +4686,32 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1" s="15" t="s">
+      <c r="A1" s="16" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="15" t="s">
+      <c r="B1" s="16" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="15" t="s">
+      <c r="C1" s="16" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="15" t="s">
+      <c r="D1" s="16" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="15" t="s">
+      <c r="E1" s="16" t="s">
         <v>148</v>
       </c>
-      <c r="F1" s="19" t="s">
+      <c r="F1" s="20" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="21"/>
+      <c r="G1" s="22"/>
     </row>
     <row r="2" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A2" s="17"/>
-      <c r="B2" s="17"/>
-      <c r="C2" s="17"/>
-      <c r="D2" s="17"/>
-      <c r="E2" s="17"/>
+      <c r="A2" s="18"/>
+      <c r="B2" s="18"/>
+      <c r="C2" s="18"/>
+      <c r="D2" s="18"/>
+      <c r="E2" s="18"/>
       <c r="F2" s="1" t="s">
         <v>149</v>
       </c>
@@ -4720,7 +4720,7 @@
       </c>
     </row>
     <row r="3" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A3" s="15" t="s">
+      <c r="A3" s="16" t="s">
         <v>151</v>
       </c>
       <c r="B3" s="1" t="s">
@@ -4743,7 +4743,7 @@
       </c>
     </row>
     <row r="4" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A4" s="16"/>
+      <c r="A4" s="17"/>
       <c r="B4" s="1" t="s">
         <v>152</v>
       </c>
@@ -4764,7 +4764,7 @@
       </c>
     </row>
     <row r="5" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A5" s="16"/>
+      <c r="A5" s="17"/>
       <c r="B5" s="1" t="s">
         <v>152</v>
       </c>
@@ -4785,7 +4785,7 @@
       </c>
     </row>
     <row r="6" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A6" s="16"/>
+      <c r="A6" s="17"/>
       <c r="B6" s="1" t="s">
         <v>152</v>
       </c>
@@ -4806,7 +4806,7 @@
       </c>
     </row>
     <row r="7" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A7" s="16"/>
+      <c r="A7" s="17"/>
       <c r="B7" s="1" t="s">
         <v>152</v>
       </c>
@@ -4827,7 +4827,7 @@
       </c>
     </row>
     <row r="8" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A8" s="16"/>
+      <c r="A8" s="17"/>
       <c r="B8" s="1" t="s">
         <v>152</v>
       </c>
@@ -4848,7 +4848,7 @@
       </c>
     </row>
     <row r="9" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A9" s="16"/>
+      <c r="A9" s="17"/>
       <c r="B9" s="1" t="s">
         <v>152</v>
       </c>
@@ -4869,7 +4869,7 @@
       </c>
     </row>
     <row r="10" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A10" s="16"/>
+      <c r="A10" s="17"/>
       <c r="B10" s="1" t="s">
         <v>160</v>
       </c>
@@ -4890,7 +4890,7 @@
       </c>
     </row>
     <row r="11" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A11" s="16"/>
+      <c r="A11" s="17"/>
       <c r="B11" s="1" t="s">
         <v>160</v>
       </c>
@@ -4911,7 +4911,7 @@
       </c>
     </row>
     <row r="12" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A12" s="16"/>
+      <c r="A12" s="17"/>
       <c r="B12" s="1" t="s">
         <v>160</v>
       </c>
@@ -4932,7 +4932,7 @@
       </c>
     </row>
     <row r="13" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A13" s="16"/>
+      <c r="A13" s="17"/>
       <c r="B13" s="1" t="s">
         <v>160</v>
       </c>
@@ -4953,7 +4953,7 @@
       </c>
     </row>
     <row r="14" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A14" s="16"/>
+      <c r="A14" s="17"/>
       <c r="B14" s="1" t="s">
         <v>160</v>
       </c>
@@ -4974,7 +4974,7 @@
       </c>
     </row>
     <row r="15" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A15" s="17"/>
+      <c r="A15" s="18"/>
       <c r="B15" s="1" t="s">
         <v>160</v>
       </c>
@@ -5045,10 +5045,10 @@
       </c>
     </row>
     <row r="2" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A2" s="15" t="s">
+      <c r="A2" s="16" t="s">
         <v>168</v>
       </c>
-      <c r="B2" s="15" t="s">
+      <c r="B2" s="16" t="s">
         <v>169</v>
       </c>
       <c r="C2" s="1" t="s">
@@ -5065,8 +5065,8 @@
       </c>
     </row>
     <row r="3" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A3" s="16"/>
-      <c r="B3" s="16"/>
+      <c r="A3" s="17"/>
+      <c r="B3" s="17"/>
       <c r="C3" s="1" t="s">
         <v>171</v>
       </c>
@@ -5081,8 +5081,8 @@
       </c>
     </row>
     <row r="4" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A4" s="16"/>
-      <c r="B4" s="16"/>
+      <c r="A4" s="17"/>
+      <c r="B4" s="17"/>
       <c r="C4" s="1" t="s">
         <v>172</v>
       </c>
@@ -5097,8 +5097,8 @@
       </c>
     </row>
     <row r="5" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A5" s="16"/>
-      <c r="B5" s="16"/>
+      <c r="A5" s="17"/>
+      <c r="B5" s="17"/>
       <c r="C5" s="1" t="s">
         <v>173</v>
       </c>
@@ -5113,8 +5113,8 @@
       </c>
     </row>
     <row r="6" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A6" s="16"/>
-      <c r="B6" s="16"/>
+      <c r="A6" s="17"/>
+      <c r="B6" s="17"/>
       <c r="C6" s="1" t="s">
         <v>174</v>
       </c>
@@ -5129,8 +5129,8 @@
       </c>
     </row>
     <row r="7" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A7" s="16"/>
-      <c r="B7" s="16"/>
+      <c r="A7" s="17"/>
+      <c r="B7" s="17"/>
       <c r="C7" s="1" t="s">
         <v>175</v>
       </c>
@@ -5145,8 +5145,8 @@
       </c>
     </row>
     <row r="8" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A8" s="16"/>
-      <c r="B8" s="16"/>
+      <c r="A8" s="17"/>
+      <c r="B8" s="17"/>
       <c r="C8" s="1" t="s">
         <v>176</v>
       </c>
@@ -5161,8 +5161,8 @@
       </c>
     </row>
     <row r="9" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A9" s="16"/>
-      <c r="B9" s="16"/>
+      <c r="A9" s="17"/>
+      <c r="B9" s="17"/>
       <c r="C9" s="1" t="s">
         <v>177</v>
       </c>
@@ -5177,8 +5177,8 @@
       </c>
     </row>
     <row r="10" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A10" s="16"/>
-      <c r="B10" s="16"/>
+      <c r="A10" s="17"/>
+      <c r="B10" s="17"/>
       <c r="C10" s="1" t="s">
         <v>178</v>
       </c>
@@ -5193,8 +5193,8 @@
       </c>
     </row>
     <row r="11" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A11" s="16"/>
-      <c r="B11" s="16"/>
+      <c r="A11" s="17"/>
+      <c r="B11" s="17"/>
       <c r="C11" s="1" t="s">
         <v>179</v>
       </c>
@@ -5209,8 +5209,8 @@
       </c>
     </row>
     <row r="12" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A12" s="17"/>
-      <c r="B12" s="17"/>
+      <c r="A12" s="18"/>
+      <c r="B12" s="18"/>
       <c r="C12" s="1" t="s">
         <v>180</v>
       </c>
@@ -5271,10 +5271,10 @@
       </c>
     </row>
     <row r="2" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A2" s="22" t="s">
+      <c r="A2" s="14" t="s">
         <v>182</v>
       </c>
-      <c r="B2" s="22" t="s">
+      <c r="B2" s="14" t="s">
         <v>183</v>
       </c>
       <c r="C2" s="9" t="s">
@@ -5291,8 +5291,8 @@
       </c>
     </row>
     <row r="3" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A3" s="23"/>
-      <c r="B3" s="23"/>
+      <c r="A3" s="15"/>
+      <c r="B3" s="15"/>
       <c r="C3" s="9" t="s">
         <v>185</v>
       </c>
@@ -5307,8 +5307,8 @@
       </c>
     </row>
     <row r="4" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A4" s="23"/>
-      <c r="B4" s="23"/>
+      <c r="A4" s="15"/>
+      <c r="B4" s="15"/>
       <c r="C4" s="9" t="s">
         <v>186</v>
       </c>
@@ -5323,8 +5323,8 @@
       </c>
     </row>
     <row r="5" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A5" s="23"/>
-      <c r="B5" s="23"/>
+      <c r="A5" s="15"/>
+      <c r="B5" s="15"/>
       <c r="C5" s="9" t="s">
         <v>187</v>
       </c>

--- a/Price and products last2.xlsx
+++ b/Price and products last2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/harshitmittal/Desktop/product_pricing_app/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{79492FAC-8781-2442-B98A-18453C3ACB64}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF265925-E72F-5C47-AAAE-89012946A569}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="780" windowWidth="36000" windowHeight="22600" firstSheet="1" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="36000" windowHeight="21000" firstSheet="1" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Chain Pulley Block" sheetId="1" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="314" uniqueCount="200">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="413" uniqueCount="249">
   <si>
     <t>Product Name</t>
   </si>
@@ -479,60 +479,15 @@
     <t>Clear Span (MM)</t>
   </si>
   <si>
-    <t>Cast Iron Wheel</t>
-  </si>
-  <si>
-    <t>Nylon Wheel</t>
-  </si>
-  <si>
     <t>Portable Gantry Crane</t>
   </si>
   <si>
     <t>Fixed Height</t>
   </si>
   <si>
-    <t>PGF1A</t>
-  </si>
-  <si>
-    <t>PGF1B</t>
-  </si>
-  <si>
-    <t>PGF2A</t>
-  </si>
-  <si>
-    <t>PGF2B</t>
-  </si>
-  <si>
-    <t>PGF3A</t>
-  </si>
-  <si>
-    <t>PGF3B</t>
-  </si>
-  <si>
-    <t>PGF5B</t>
-  </si>
-  <si>
     <t>Adjustable Height</t>
   </si>
   <si>
-    <t>PGA1</t>
-  </si>
-  <si>
-    <t>PGA2</t>
-  </si>
-  <si>
-    <t>PGA3</t>
-  </si>
-  <si>
-    <t>PGA5</t>
-  </si>
-  <si>
-    <t>PGA7.5</t>
-  </si>
-  <si>
-    <t>PGA10</t>
-  </si>
-  <si>
     <t>Total Height(MM)</t>
   </si>
   <si>
@@ -630,13 +585,205 @@
   </si>
   <si>
     <t>HJC2</t>
+  </si>
+  <si>
+    <t>EF1S1H1</t>
+  </si>
+  <si>
+    <t>EF1S1H2</t>
+  </si>
+  <si>
+    <t>EF1S1H3</t>
+  </si>
+  <si>
+    <t>EF1S1H4</t>
+  </si>
+  <si>
+    <t>EF1S2H1</t>
+  </si>
+  <si>
+    <t>EF1S2H2</t>
+  </si>
+  <si>
+    <t>EF1S2H3</t>
+  </si>
+  <si>
+    <t>EF1S2H4</t>
+  </si>
+  <si>
+    <t>EF1S3H1</t>
+  </si>
+  <si>
+    <t>EF1S3H2</t>
+  </si>
+  <si>
+    <t>EF1S3H3</t>
+  </si>
+  <si>
+    <t>EF1S3H4</t>
+  </si>
+  <si>
+    <t>EF2S1H1</t>
+  </si>
+  <si>
+    <t>EF2S1H2</t>
+  </si>
+  <si>
+    <t>EF2S1H3</t>
+  </si>
+  <si>
+    <t>EF2S1H4</t>
+  </si>
+  <si>
+    <t>EF2S2H1</t>
+  </si>
+  <si>
+    <t>EF2S2H2</t>
+  </si>
+  <si>
+    <t>EF2S2H3</t>
+  </si>
+  <si>
+    <t>EF2S2H4</t>
+  </si>
+  <si>
+    <t>EF2S3H1</t>
+  </si>
+  <si>
+    <t>EF2S3H2</t>
+  </si>
+  <si>
+    <t>EF2S3H3</t>
+  </si>
+  <si>
+    <t>EF2S3H4</t>
+  </si>
+  <si>
+    <t>EF3S1H1</t>
+  </si>
+  <si>
+    <t>EF3S1H2</t>
+  </si>
+  <si>
+    <t>EF3S1H3</t>
+  </si>
+  <si>
+    <t>EF3S1H4</t>
+  </si>
+  <si>
+    <t>EF3S2H1</t>
+  </si>
+  <si>
+    <t>EF3S2H2</t>
+  </si>
+  <si>
+    <t>EF3S2H3</t>
+  </si>
+  <si>
+    <t>EF3S2H4</t>
+  </si>
+  <si>
+    <t>EF3S3H1</t>
+  </si>
+  <si>
+    <t>EF3S3H2</t>
+  </si>
+  <si>
+    <t>EF3S3H3</t>
+  </si>
+  <si>
+    <t>EF3S3H4</t>
+  </si>
+  <si>
+    <t>Under Beam Height (MM)</t>
+  </si>
+  <si>
+    <t>EA1S1H1</t>
+  </si>
+  <si>
+    <t>EA1S1H2</t>
+  </si>
+  <si>
+    <t>EA1S1H3</t>
+  </si>
+  <si>
+    <t>EA1S2H1</t>
+  </si>
+  <si>
+    <t>EA1S2H2</t>
+  </si>
+  <si>
+    <t>EA1S2H3</t>
+  </si>
+  <si>
+    <t>EA1S3H1</t>
+  </si>
+  <si>
+    <t>EA1S3H2</t>
+  </si>
+  <si>
+    <t>EA1S3H3</t>
+  </si>
+  <si>
+    <t>EA2S1H1</t>
+  </si>
+  <si>
+    <t>EA2S1H2</t>
+  </si>
+  <si>
+    <t>EA2S1H3</t>
+  </si>
+  <si>
+    <t>EA2S2H1</t>
+  </si>
+  <si>
+    <t>EA2S2H2</t>
+  </si>
+  <si>
+    <t>EA2S2H3</t>
+  </si>
+  <si>
+    <t>EA2S3H1</t>
+  </si>
+  <si>
+    <t>EA2S3H2</t>
+  </si>
+  <si>
+    <t>EA2S3H3</t>
+  </si>
+  <si>
+    <t>EA3S1H1</t>
+  </si>
+  <si>
+    <t>EA3S1H2</t>
+  </si>
+  <si>
+    <t>EA3S1H3</t>
+  </si>
+  <si>
+    <t>EA3S2H1</t>
+  </si>
+  <si>
+    <t>EA3S2H2</t>
+  </si>
+  <si>
+    <t>EA3S2H3</t>
+  </si>
+  <si>
+    <t>EA3S3H1</t>
+  </si>
+  <si>
+    <t>EA3S3H2</t>
+  </si>
+  <si>
+    <t>EA3S3H3</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -669,6 +816,12 @@
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
       <name val="Arial"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -818,7 +971,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -859,11 +1012,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
@@ -876,6 +1029,10 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -883,6 +1040,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1135,10 +1295,10 @@
       </c>
     </row>
     <row r="2" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A2" s="16" t="s">
+      <c r="A2" s="15" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="16" t="s">
+      <c r="B2" s="15" t="s">
         <v>7</v>
       </c>
       <c r="C2" s="1" t="s">
@@ -1236,7 +1396,7 @@
     </row>
     <row r="8" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A8" s="17"/>
-      <c r="B8" s="16" t="s">
+      <c r="B8" s="15" t="s">
         <v>14</v>
       </c>
       <c r="C8" s="1" t="s">
@@ -1398,7 +1558,7 @@
     </row>
     <row r="18" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A18" s="17"/>
-      <c r="B18" s="16" t="s">
+      <c r="B18" s="15" t="s">
         <v>18</v>
       </c>
       <c r="C18" s="1" t="s">
@@ -1496,7 +1656,7 @@
     </row>
     <row r="24" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A24" s="17"/>
-      <c r="B24" s="16" t="s">
+      <c r="B24" s="15" t="s">
         <v>21</v>
       </c>
       <c r="C24" s="1" t="s">
@@ -1591,14 +1751,14 @@
       <c r="F1" s="10"/>
     </row>
     <row r="2" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A2" s="14" t="s">
-        <v>188</v>
-      </c>
-      <c r="B2" s="23" t="s">
-        <v>191</v>
+      <c r="A2" s="23" t="s">
+        <v>173</v>
+      </c>
+      <c r="B2" s="25" t="s">
+        <v>176</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>189</v>
+        <v>174</v>
       </c>
       <c r="D2" s="9">
         <v>1</v>
@@ -1609,10 +1769,10 @@
       <c r="F2" s="10"/>
     </row>
     <row r="3" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A3" s="14"/>
-      <c r="B3" s="24"/>
+      <c r="A3" s="23"/>
+      <c r="B3" s="26"/>
       <c r="C3" s="9" t="s">
-        <v>190</v>
+        <v>175</v>
       </c>
       <c r="D3" s="9">
         <v>1.5</v>
@@ -1623,12 +1783,12 @@
       <c r="F3" s="10"/>
     </row>
     <row r="4" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A4" s="14"/>
-      <c r="B4" s="25" t="s">
-        <v>192</v>
+      <c r="A4" s="23"/>
+      <c r="B4" s="27" t="s">
+        <v>177</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>193</v>
+        <v>178</v>
       </c>
       <c r="D4" s="13">
         <v>1</v>
@@ -1639,10 +1799,10 @@
       <c r="F4" s="10"/>
     </row>
     <row r="5" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A5" s="14"/>
-      <c r="B5" s="25"/>
+      <c r="A5" s="23"/>
+      <c r="B5" s="27"/>
       <c r="C5" s="11" t="s">
-        <v>194</v>
+        <v>179</v>
       </c>
       <c r="D5" s="11">
         <v>1.5</v>
@@ -1687,21 +1847,21 @@
         <v>2</v>
       </c>
       <c r="D1" s="12" t="s">
-        <v>195</v>
+        <v>180</v>
       </c>
       <c r="E1" s="12" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A2" s="25" t="s">
-        <v>196</v>
-      </c>
-      <c r="B2" s="25" t="s">
-        <v>197</v>
+      <c r="A2" s="27" t="s">
+        <v>181</v>
+      </c>
+      <c r="B2" s="27" t="s">
+        <v>182</v>
       </c>
       <c r="C2" s="12" t="s">
-        <v>198</v>
+        <v>183</v>
       </c>
       <c r="D2" s="13">
         <v>1</v>
@@ -1711,10 +1871,10 @@
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A3" s="25"/>
-      <c r="B3" s="25"/>
+      <c r="A3" s="27"/>
+      <c r="B3" s="27"/>
       <c r="C3" s="12" t="s">
-        <v>199</v>
+        <v>184</v>
       </c>
       <c r="D3" s="13">
         <v>2</v>
@@ -1769,10 +1929,10 @@
       </c>
     </row>
     <row r="2" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A2" s="16" t="s">
+      <c r="A2" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="B2" s="16" t="s">
+      <c r="B2" s="15" t="s">
         <v>24</v>
       </c>
       <c r="C2" s="1" t="s">
@@ -1886,7 +2046,7 @@
     </row>
     <row r="9" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A9" s="17"/>
-      <c r="B9" s="16" t="s">
+      <c r="B9" s="15" t="s">
         <v>32</v>
       </c>
       <c r="C9" s="1" t="s">
@@ -1968,7 +2128,7 @@
     </row>
     <row r="14" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A14" s="17"/>
-      <c r="B14" s="16" t="s">
+      <c r="B14" s="15" t="s">
         <v>33</v>
       </c>
       <c r="C14" s="1" t="s">
@@ -2067,10 +2227,10 @@
       </c>
     </row>
     <row r="2" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A2" s="16" t="s">
+      <c r="A2" s="15" t="s">
         <v>38</v>
       </c>
-      <c r="B2" s="16" t="s">
+      <c r="B2" s="15" t="s">
         <v>39</v>
       </c>
       <c r="C2" s="1" t="s">
@@ -2111,7 +2271,7 @@
     </row>
     <row r="5" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A5" s="17"/>
-      <c r="B5" s="16" t="s">
+      <c r="B5" s="15" t="s">
         <v>43</v>
       </c>
       <c r="C5" s="1" t="s">
@@ -2256,7 +2416,7 @@
       <c r="A2" s="19" t="s">
         <v>38</v>
       </c>
-      <c r="B2" s="16" t="s">
+      <c r="B2" s="15" t="s">
         <v>55</v>
       </c>
       <c r="C2" s="3" t="s">
@@ -3136,19 +3296,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A1" s="16" t="s">
+      <c r="A1" s="15" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="16" t="s">
+      <c r="B1" s="15" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="16" t="s">
+      <c r="C1" s="15" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="16" t="s">
+      <c r="D1" s="15" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="16" t="s">
+      <c r="E1" s="15" t="s">
         <v>99</v>
       </c>
       <c r="F1" s="20" t="s">
@@ -3192,10 +3352,10 @@
       <c r="N2" s="5"/>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A3" s="16" t="s">
+      <c r="A3" s="15" t="s">
         <v>104</v>
       </c>
-      <c r="B3" s="16" t="s">
+      <c r="B3" s="15" t="s">
         <v>105</v>
       </c>
       <c r="C3" s="1" t="s">
@@ -3366,19 +3526,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1" s="16" t="s">
+      <c r="A1" s="15" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="16" t="s">
+      <c r="B1" s="15" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="16" t="s">
+      <c r="C1" s="15" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="16" t="s">
+      <c r="D1" s="15" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="16" t="s">
+      <c r="E1" s="15" t="s">
         <v>99</v>
       </c>
       <c r="F1" s="20" t="s">
@@ -3431,7 +3591,7 @@
       <c r="A3" s="19" t="s">
         <v>104</v>
       </c>
-      <c r="B3" s="16" t="s">
+      <c r="B3" s="15" t="s">
         <v>115</v>
       </c>
       <c r="C3" s="2" t="s">
@@ -4673,61 +4833,71 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:G15"/>
+  <dimension ref="A1:G64"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="17.5" customWidth="1"/>
     <col min="2" max="2" width="14.1640625" customWidth="1"/>
-    <col min="3" max="3" width="6.5" customWidth="1"/>
+    <col min="3" max="3" width="7.83203125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="11.6640625" customWidth="1"/>
     <col min="5" max="5" width="13.5" customWidth="1"/>
-    <col min="6" max="6" width="12.83203125" customWidth="1"/>
+    <col min="6" max="6" width="20.5" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="10.6640625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1" s="16" t="s">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="16" t="s">
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="16" t="s">
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="16" t="s">
+      <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="16" t="s">
+      <c r="E1" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="F1" s="20" t="s">
+      <c r="F1" s="7" t="s">
+        <v>221</v>
+      </c>
+      <c r="G1" s="14" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="22"/>
     </row>
     <row r="2" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A2" s="18"/>
-      <c r="B2" s="18"/>
-      <c r="C2" s="18"/>
-      <c r="D2" s="18"/>
-      <c r="E2" s="18"/>
-      <c r="F2" s="1" t="s">
+      <c r="A2" s="15" t="s">
         <v>149</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="B2" s="1" t="s">
         <v>150</v>
       </c>
+      <c r="C2" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="D2" s="1">
+        <v>1</v>
+      </c>
+      <c r="E2" s="1">
+        <v>3000</v>
+      </c>
+      <c r="F2" s="1">
+        <v>2300</v>
+      </c>
+      <c r="G2" s="1">
+        <v>56330</v>
+      </c>
     </row>
     <row r="3" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A3" s="16" t="s">
-        <v>151</v>
-      </c>
+      <c r="A3" s="16"/>
       <c r="B3" s="1" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>153</v>
+        <v>186</v>
       </c>
       <c r="D3" s="1">
         <v>1</v>
@@ -4736,7 +4906,7 @@
         <v>3000</v>
       </c>
       <c r="F3" s="1">
-        <v>60600</v>
+        <v>3300</v>
       </c>
       <c r="G3" s="1">
         <v>56330</v>
@@ -4745,19 +4915,19 @@
     <row r="4" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A4" s="17"/>
       <c r="B4" s="1" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>154</v>
+        <v>187</v>
       </c>
       <c r="D4" s="1">
         <v>1</v>
       </c>
       <c r="E4" s="1">
-        <v>3500</v>
+        <v>3000</v>
       </c>
       <c r="F4" s="1">
-        <v>91550</v>
+        <v>4300</v>
       </c>
       <c r="G4" s="1">
         <v>87280</v>
@@ -4766,245 +4936,1270 @@
     <row r="5" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A5" s="17"/>
       <c r="B5" s="1" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>155</v>
+        <v>188</v>
       </c>
       <c r="D5" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E5" s="1">
         <v>3000</v>
       </c>
       <c r="F5" s="1">
-        <v>67075</v>
+        <v>5300</v>
       </c>
       <c r="G5" s="1">
-        <v>63235</v>
+        <v>87280</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A6" s="17"/>
       <c r="B6" s="1" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>156</v>
+        <v>189</v>
       </c>
       <c r="D6" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E6" s="1">
-        <v>3500</v>
+        <v>4500</v>
       </c>
       <c r="F6" s="1">
-        <v>99635</v>
+        <v>2300</v>
       </c>
       <c r="G6" s="1">
-        <v>95800</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A7" s="17"/>
       <c r="B7" s="1" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>157</v>
+        <v>190</v>
       </c>
       <c r="D7" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E7" s="1">
-        <v>3000</v>
+        <v>4500</v>
       </c>
       <c r="F7" s="1">
-        <v>77090</v>
+        <v>3300</v>
       </c>
       <c r="G7" s="1">
-        <v>83355</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A8" s="17"/>
       <c r="B8" s="1" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>158</v>
+        <v>191</v>
       </c>
       <c r="D8" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E8" s="1">
-        <v>3500</v>
+        <v>4500</v>
       </c>
       <c r="F8" s="1">
-        <v>123490</v>
+        <v>4300</v>
       </c>
       <c r="G8" s="1">
-        <v>129870</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A9" s="17"/>
       <c r="B9" s="1" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>159</v>
+        <v>192</v>
       </c>
       <c r="D9" s="1">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E9" s="1">
-        <v>3500</v>
+        <v>4500</v>
       </c>
       <c r="F9" s="1">
-        <v>168825</v>
+        <v>5300</v>
       </c>
       <c r="G9" s="1">
-        <v>182735</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A10" s="17"/>
       <c r="B10" s="1" t="s">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>161</v>
+        <v>193</v>
       </c>
       <c r="D10" s="1">
         <v>1</v>
       </c>
       <c r="E10" s="1">
-        <v>3500</v>
+        <v>6000</v>
       </c>
       <c r="F10" s="1">
-        <v>115325</v>
+        <v>2300</v>
       </c>
       <c r="G10" s="1">
-        <v>110365</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A11" s="17"/>
       <c r="B11" s="1" t="s">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>162</v>
+        <v>194</v>
       </c>
       <c r="D11" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E11" s="1">
-        <v>3500</v>
+        <v>6000</v>
       </c>
       <c r="F11" s="1">
-        <v>121650</v>
+        <v>3300</v>
       </c>
       <c r="G11" s="1">
-        <v>138265</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A12" s="17"/>
       <c r="B12" s="1" t="s">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>163</v>
+        <v>195</v>
       </c>
       <c r="D12" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E12" s="1">
-        <v>3500</v>
+        <v>6000</v>
       </c>
       <c r="F12" s="1">
-        <v>157720</v>
+        <v>4300</v>
       </c>
       <c r="G12" s="1">
-        <v>164165</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A13" s="17"/>
       <c r="B13" s="1" t="s">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>164</v>
+        <v>196</v>
       </c>
       <c r="D13" s="1">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E13" s="1">
-        <v>3500</v>
+        <v>6000</v>
       </c>
       <c r="F13" s="1">
-        <v>218075</v>
+        <v>5300</v>
       </c>
       <c r="G13" s="1">
-        <v>227000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A14" s="17"/>
       <c r="B14" s="1" t="s">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>165</v>
+        <v>197</v>
       </c>
       <c r="D14" s="1">
-        <v>7.5</v>
+        <v>2</v>
       </c>
       <c r="E14" s="1">
-        <v>3500</v>
+        <v>3000</v>
       </c>
       <c r="F14" s="1">
-        <v>283035</v>
+        <v>2300</v>
       </c>
       <c r="G14" s="1">
-        <v>299175</v>
+        <v>63235</v>
       </c>
     </row>
     <row r="15" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A15" s="18"/>
+      <c r="A15" s="17"/>
       <c r="B15" s="1" t="s">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>166</v>
+        <v>198</v>
       </c>
       <c r="D15" s="1">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="E15" s="1">
-        <v>3500</v>
+        <v>3000</v>
       </c>
       <c r="F15" s="1">
-        <v>301090</v>
+        <v>3300</v>
       </c>
       <c r="G15" s="1">
-        <v>407545</v>
+        <v>63235</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A16" s="17"/>
+      <c r="B16" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="D16" s="1">
+        <v>2</v>
+      </c>
+      <c r="E16" s="1">
+        <v>3000</v>
+      </c>
+      <c r="F16" s="1">
+        <v>4300</v>
+      </c>
+      <c r="G16" s="1">
+        <v>95800</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A17" s="17"/>
+      <c r="B17" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="D17" s="1">
+        <v>2</v>
+      </c>
+      <c r="E17" s="1">
+        <v>3000</v>
+      </c>
+      <c r="F17" s="1">
+        <v>5300</v>
+      </c>
+      <c r="G17" s="1">
+        <v>95800</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A18" s="17"/>
+      <c r="B18" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="D18" s="1">
+        <v>2</v>
+      </c>
+      <c r="E18" s="1">
+        <v>4500</v>
+      </c>
+      <c r="F18" s="1">
+        <v>2300</v>
+      </c>
+      <c r="G18" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A19" s="17"/>
+      <c r="B19" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="D19" s="1">
+        <v>2</v>
+      </c>
+      <c r="E19" s="1">
+        <v>4500</v>
+      </c>
+      <c r="F19" s="1">
+        <v>3300</v>
+      </c>
+      <c r="G19" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A20" s="17"/>
+      <c r="B20" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="D20" s="1">
+        <v>2</v>
+      </c>
+      <c r="E20" s="1">
+        <v>4500</v>
+      </c>
+      <c r="F20" s="1">
+        <v>4300</v>
+      </c>
+      <c r="G20" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A21" s="17"/>
+      <c r="B21" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="D21" s="1">
+        <v>2</v>
+      </c>
+      <c r="E21" s="1">
+        <v>4500</v>
+      </c>
+      <c r="F21" s="1">
+        <v>5300</v>
+      </c>
+      <c r="G21" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A22" s="17"/>
+      <c r="B22" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="D22" s="1">
+        <v>2</v>
+      </c>
+      <c r="E22" s="1">
+        <v>6000</v>
+      </c>
+      <c r="F22" s="1">
+        <v>2300</v>
+      </c>
+      <c r="G22" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A23" s="17"/>
+      <c r="B23" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="D23" s="1">
+        <v>2</v>
+      </c>
+      <c r="E23" s="1">
+        <v>6000</v>
+      </c>
+      <c r="F23" s="1">
+        <v>3300</v>
+      </c>
+      <c r="G23" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A24" s="17"/>
+      <c r="B24" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="D24" s="1">
+        <v>2</v>
+      </c>
+      <c r="E24" s="1">
+        <v>6000</v>
+      </c>
+      <c r="F24" s="1">
+        <v>4300</v>
+      </c>
+      <c r="G24" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A25" s="17"/>
+      <c r="B25" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="D25" s="1">
+        <v>2</v>
+      </c>
+      <c r="E25" s="1">
+        <v>6000</v>
+      </c>
+      <c r="F25" s="1">
+        <v>5300</v>
+      </c>
+      <c r="G25" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A26" s="17"/>
+      <c r="B26" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="D26" s="1">
+        <v>3</v>
+      </c>
+      <c r="E26" s="1">
+        <v>3000</v>
+      </c>
+      <c r="F26" s="1">
+        <v>2300</v>
+      </c>
+      <c r="G26" s="1">
+        <v>83355</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A27" s="17"/>
+      <c r="B27" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="D27" s="1">
+        <v>3</v>
+      </c>
+      <c r="E27" s="1">
+        <v>3000</v>
+      </c>
+      <c r="F27" s="1">
+        <v>3300</v>
+      </c>
+      <c r="G27" s="1">
+        <v>83355</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A28" s="17"/>
+      <c r="B28" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="D28" s="1">
+        <v>3</v>
+      </c>
+      <c r="E28" s="1">
+        <v>3000</v>
+      </c>
+      <c r="F28" s="1">
+        <v>4300</v>
+      </c>
+      <c r="G28" s="1">
+        <v>129870</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A29" s="17"/>
+      <c r="B29" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="D29" s="1">
+        <v>3</v>
+      </c>
+      <c r="E29" s="1">
+        <v>3000</v>
+      </c>
+      <c r="F29" s="1">
+        <v>5300</v>
+      </c>
+      <c r="G29" s="1">
+        <v>129870</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A30" s="17"/>
+      <c r="B30" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="D30" s="1">
+        <v>3</v>
+      </c>
+      <c r="E30" s="1">
+        <v>4500</v>
+      </c>
+      <c r="F30" s="1">
+        <v>2300</v>
+      </c>
+      <c r="G30" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A31" s="17"/>
+      <c r="B31" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="D31" s="1">
+        <v>3</v>
+      </c>
+      <c r="E31" s="1">
+        <v>4500</v>
+      </c>
+      <c r="F31" s="1">
+        <v>3300</v>
+      </c>
+      <c r="G31" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A32" s="17"/>
+      <c r="B32" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="D32" s="1">
+        <v>3</v>
+      </c>
+      <c r="E32" s="1">
+        <v>4500</v>
+      </c>
+      <c r="F32" s="1">
+        <v>4300</v>
+      </c>
+      <c r="G32" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A33" s="17"/>
+      <c r="B33" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="D33" s="1">
+        <v>3</v>
+      </c>
+      <c r="E33" s="1">
+        <v>4500</v>
+      </c>
+      <c r="F33" s="1">
+        <v>5300</v>
+      </c>
+      <c r="G33" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A34" s="17"/>
+      <c r="B34" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="D34" s="1">
+        <v>3</v>
+      </c>
+      <c r="E34" s="1">
+        <v>6000</v>
+      </c>
+      <c r="F34" s="1">
+        <v>2300</v>
+      </c>
+      <c r="G34" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A35" s="17"/>
+      <c r="B35" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="C35" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="D35" s="1">
+        <v>3</v>
+      </c>
+      <c r="E35" s="1">
+        <v>6000</v>
+      </c>
+      <c r="F35" s="1">
+        <v>3300</v>
+      </c>
+      <c r="G35" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A36" s="17"/>
+      <c r="B36" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="C36" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="D36" s="1">
+        <v>3</v>
+      </c>
+      <c r="E36" s="1">
+        <v>6000</v>
+      </c>
+      <c r="F36" s="1">
+        <v>4300</v>
+      </c>
+      <c r="G36" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A37" s="17"/>
+      <c r="B37" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="C37" s="1" t="s">
+        <v>220</v>
+      </c>
+      <c r="D37" s="1">
+        <v>3</v>
+      </c>
+      <c r="E37" s="1">
+        <v>6000</v>
+      </c>
+      <c r="F37" s="1">
+        <v>5300</v>
+      </c>
+      <c r="G37" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A38" s="17"/>
+      <c r="B38" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="C38" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="D38" s="1">
+        <v>1</v>
+      </c>
+      <c r="E38" s="1">
+        <v>3000</v>
+      </c>
+      <c r="F38" s="1">
+        <v>3100</v>
+      </c>
+      <c r="G38" s="1">
+        <v>110365</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A39" s="17"/>
+      <c r="B39" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="C39" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="D39" s="1">
+        <v>1</v>
+      </c>
+      <c r="E39" s="1">
+        <v>3000</v>
+      </c>
+      <c r="F39" s="1">
+        <v>4200</v>
+      </c>
+      <c r="G39" s="1">
+        <v>110365</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A40" s="17"/>
+      <c r="B40" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="C40" s="1" t="s">
+        <v>224</v>
+      </c>
+      <c r="D40" s="1">
+        <v>1</v>
+      </c>
+      <c r="E40" s="1">
+        <v>3000</v>
+      </c>
+      <c r="F40" s="1">
+        <v>5200</v>
+      </c>
+      <c r="G40" s="1">
+        <v>110365</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A41" s="17"/>
+      <c r="B41" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="C41" s="1" t="s">
+        <v>225</v>
+      </c>
+      <c r="D41" s="1">
+        <v>1</v>
+      </c>
+      <c r="E41" s="1">
+        <v>4500</v>
+      </c>
+      <c r="F41" s="1">
+        <v>3100</v>
+      </c>
+      <c r="G41" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A42" s="17"/>
+      <c r="B42" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="C42" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="D42" s="1">
+        <v>1</v>
+      </c>
+      <c r="E42" s="1">
+        <v>4500</v>
+      </c>
+      <c r="F42" s="1">
+        <v>4200</v>
+      </c>
+      <c r="G42" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A43" s="17"/>
+      <c r="B43" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="C43" s="1" t="s">
+        <v>227</v>
+      </c>
+      <c r="D43" s="1">
+        <v>1</v>
+      </c>
+      <c r="E43" s="1">
+        <v>4500</v>
+      </c>
+      <c r="F43" s="1">
+        <v>5200</v>
+      </c>
+      <c r="G43" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A44" s="17"/>
+      <c r="B44" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="C44" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="D44" s="1">
+        <v>1</v>
+      </c>
+      <c r="E44" s="1">
+        <v>6000</v>
+      </c>
+      <c r="F44" s="1">
+        <v>3100</v>
+      </c>
+      <c r="G44" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A45" s="17"/>
+      <c r="B45" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="C45" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="D45" s="1">
+        <v>1</v>
+      </c>
+      <c r="E45" s="1">
+        <v>6000</v>
+      </c>
+      <c r="F45" s="1">
+        <v>4200</v>
+      </c>
+      <c r="G45" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A46" s="17"/>
+      <c r="B46" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="C46" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="D46" s="1">
+        <v>1</v>
+      </c>
+      <c r="E46" s="1">
+        <v>6000</v>
+      </c>
+      <c r="F46" s="1">
+        <v>5200</v>
+      </c>
+      <c r="G46" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A47" s="17"/>
+      <c r="B47" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="C47" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="D47" s="1">
+        <v>2</v>
+      </c>
+      <c r="E47" s="1">
+        <v>3000</v>
+      </c>
+      <c r="F47" s="1">
+        <v>3100</v>
+      </c>
+      <c r="G47" s="1">
+        <v>138265</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A48" s="17"/>
+      <c r="B48" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="C48" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="D48" s="1">
+        <v>2</v>
+      </c>
+      <c r="E48" s="1">
+        <v>3000</v>
+      </c>
+      <c r="F48" s="1">
+        <v>4200</v>
+      </c>
+      <c r="G48" s="1">
+        <v>138265</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A49" s="17"/>
+      <c r="B49" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="C49" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="D49" s="1">
+        <v>2</v>
+      </c>
+      <c r="E49" s="1">
+        <v>3000</v>
+      </c>
+      <c r="F49" s="1">
+        <v>5200</v>
+      </c>
+      <c r="G49" s="1">
+        <v>138265</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A50" s="17"/>
+      <c r="B50" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="C50" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="D50" s="1">
+        <v>2</v>
+      </c>
+      <c r="E50" s="1">
+        <v>4500</v>
+      </c>
+      <c r="F50" s="1">
+        <v>3100</v>
+      </c>
+      <c r="G50" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A51" s="17"/>
+      <c r="B51" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="C51" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="D51" s="1">
+        <v>2</v>
+      </c>
+      <c r="E51" s="1">
+        <v>4500</v>
+      </c>
+      <c r="F51" s="1">
+        <v>4200</v>
+      </c>
+      <c r="G51" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A52" s="17"/>
+      <c r="B52" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="C52" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="D52" s="1">
+        <v>2</v>
+      </c>
+      <c r="E52" s="1">
+        <v>4500</v>
+      </c>
+      <c r="F52" s="1">
+        <v>5200</v>
+      </c>
+      <c r="G52" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A53" s="17"/>
+      <c r="B53" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="C53" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="D53" s="1">
+        <v>2</v>
+      </c>
+      <c r="E53" s="28">
+        <v>6000</v>
+      </c>
+      <c r="F53" s="1">
+        <v>3100</v>
+      </c>
+      <c r="G53" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A54" s="17"/>
+      <c r="B54" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="C54" s="1" t="s">
+        <v>238</v>
+      </c>
+      <c r="D54" s="1">
+        <v>2</v>
+      </c>
+      <c r="E54" s="28">
+        <v>6000</v>
+      </c>
+      <c r="F54" s="1">
+        <v>4200</v>
+      </c>
+      <c r="G54" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A55" s="17"/>
+      <c r="B55" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="C55" s="1" t="s">
+        <v>239</v>
+      </c>
+      <c r="D55" s="1">
+        <v>2</v>
+      </c>
+      <c r="E55" s="1">
+        <v>6000</v>
+      </c>
+      <c r="F55" s="1">
+        <v>5200</v>
+      </c>
+      <c r="G55" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A56" s="17"/>
+      <c r="B56" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="C56" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="D56" s="1">
+        <v>3</v>
+      </c>
+      <c r="E56" s="1">
+        <v>3000</v>
+      </c>
+      <c r="F56" s="1">
+        <v>3650</v>
+      </c>
+      <c r="G56" s="1">
+        <v>164165</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A57" s="17"/>
+      <c r="B57" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="C57" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="D57" s="1">
+        <v>3</v>
+      </c>
+      <c r="E57" s="1">
+        <v>3000</v>
+      </c>
+      <c r="F57" s="1">
+        <v>4750</v>
+      </c>
+      <c r="G57" s="1">
+        <v>164165</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A58" s="17"/>
+      <c r="B58" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="C58" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="D58" s="1">
+        <v>3</v>
+      </c>
+      <c r="E58" s="1">
+        <v>3000</v>
+      </c>
+      <c r="F58" s="1">
+        <v>5750</v>
+      </c>
+      <c r="G58" s="1">
+        <v>164165</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A59" s="17"/>
+      <c r="B59" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="C59" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="D59" s="1">
+        <v>3</v>
+      </c>
+      <c r="E59" s="1">
+        <v>4500</v>
+      </c>
+      <c r="F59" s="1">
+        <v>3650</v>
+      </c>
+      <c r="G59" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A60" s="17"/>
+      <c r="B60" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="C60" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="D60" s="1">
+        <v>3</v>
+      </c>
+      <c r="E60" s="1">
+        <v>4500</v>
+      </c>
+      <c r="F60" s="1">
+        <v>4750</v>
+      </c>
+      <c r="G60" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A61" s="17"/>
+      <c r="B61" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="C61" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="D61" s="1">
+        <v>3</v>
+      </c>
+      <c r="E61" s="1">
+        <v>4500</v>
+      </c>
+      <c r="F61" s="1">
+        <v>5750</v>
+      </c>
+      <c r="G61" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A62" s="17"/>
+      <c r="B62" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="C62" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="D62" s="1">
+        <v>3</v>
+      </c>
+      <c r="E62" s="1">
+        <v>6000</v>
+      </c>
+      <c r="F62" s="1">
+        <v>3650</v>
+      </c>
+      <c r="G62" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A63" s="17"/>
+      <c r="B63" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="C63" s="1" t="s">
+        <v>247</v>
+      </c>
+      <c r="D63" s="1">
+        <v>3</v>
+      </c>
+      <c r="E63" s="1">
+        <v>6000</v>
+      </c>
+      <c r="F63" s="1">
+        <v>4750</v>
+      </c>
+      <c r="G63" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A64" s="18"/>
+      <c r="B64" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="C64" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="D64" s="1">
+        <v>3</v>
+      </c>
+      <c r="E64" s="1">
+        <v>6000</v>
+      </c>
+      <c r="F64" s="1">
+        <v>5750</v>
+      </c>
+      <c r="G64" s="1">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="7">
-    <mergeCell ref="F1:G1"/>
-    <mergeCell ref="A3:A15"/>
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:B2"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="D1:D2"/>
-    <mergeCell ref="E1:E2"/>
+  <mergeCells count="1">
+    <mergeCell ref="A2:A64"/>
   </mergeCells>
+  <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
 </file>
 
@@ -5038,21 +6233,21 @@
         <v>3</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>167</v>
+        <v>152</v>
       </c>
       <c r="F1" s="8" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A2" s="16" t="s">
-        <v>168</v>
-      </c>
-      <c r="B2" s="16" t="s">
-        <v>169</v>
+      <c r="A2" s="15" t="s">
+        <v>153</v>
+      </c>
+      <c r="B2" s="15" t="s">
+        <v>154</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>170</v>
+        <v>155</v>
       </c>
       <c r="D2" s="4">
         <v>1</v>
@@ -5068,7 +6263,7 @@
       <c r="A3" s="17"/>
       <c r="B3" s="17"/>
       <c r="C3" s="1" t="s">
-        <v>171</v>
+        <v>156</v>
       </c>
       <c r="D3" s="4">
         <v>1</v>
@@ -5084,7 +6279,7 @@
       <c r="A4" s="17"/>
       <c r="B4" s="17"/>
       <c r="C4" s="1" t="s">
-        <v>172</v>
+        <v>157</v>
       </c>
       <c r="D4" s="4">
         <v>1</v>
@@ -5100,7 +6295,7 @@
       <c r="A5" s="17"/>
       <c r="B5" s="17"/>
       <c r="C5" s="1" t="s">
-        <v>173</v>
+        <v>158</v>
       </c>
       <c r="D5" s="4">
         <v>2</v>
@@ -5116,7 +6311,7 @@
       <c r="A6" s="17"/>
       <c r="B6" s="17"/>
       <c r="C6" s="1" t="s">
-        <v>174</v>
+        <v>159</v>
       </c>
       <c r="D6" s="4">
         <v>2</v>
@@ -5132,7 +6327,7 @@
       <c r="A7" s="17"/>
       <c r="B7" s="17"/>
       <c r="C7" s="1" t="s">
-        <v>175</v>
+        <v>160</v>
       </c>
       <c r="D7" s="4">
         <v>2</v>
@@ -5148,7 +6343,7 @@
       <c r="A8" s="17"/>
       <c r="B8" s="17"/>
       <c r="C8" s="1" t="s">
-        <v>176</v>
+        <v>161</v>
       </c>
       <c r="D8" s="4">
         <v>3</v>
@@ -5164,7 +6359,7 @@
       <c r="A9" s="17"/>
       <c r="B9" s="17"/>
       <c r="C9" s="1" t="s">
-        <v>177</v>
+        <v>162</v>
       </c>
       <c r="D9" s="4">
         <v>3</v>
@@ -5180,7 +6375,7 @@
       <c r="A10" s="17"/>
       <c r="B10" s="17"/>
       <c r="C10" s="1" t="s">
-        <v>178</v>
+        <v>163</v>
       </c>
       <c r="D10" s="4">
         <v>3</v>
@@ -5196,7 +6391,7 @@
       <c r="A11" s="17"/>
       <c r="B11" s="17"/>
       <c r="C11" s="1" t="s">
-        <v>179</v>
+        <v>164</v>
       </c>
       <c r="D11" s="4">
         <v>5</v>
@@ -5212,7 +6407,7 @@
       <c r="A12" s="18"/>
       <c r="B12" s="18"/>
       <c r="C12" s="1" t="s">
-        <v>180</v>
+        <v>165</v>
       </c>
       <c r="D12" s="4">
         <v>5</v>
@@ -5264,21 +6459,21 @@
         <v>3</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>181</v>
+        <v>166</v>
       </c>
       <c r="F1" s="3" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A2" s="14" t="s">
-        <v>182</v>
-      </c>
-      <c r="B2" s="14" t="s">
-        <v>183</v>
+      <c r="A2" s="23" t="s">
+        <v>167</v>
+      </c>
+      <c r="B2" s="23" t="s">
+        <v>168</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>184</v>
+        <v>169</v>
       </c>
       <c r="D2" s="9">
         <v>1.5</v>
@@ -5291,10 +6486,10 @@
       </c>
     </row>
     <row r="3" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A3" s="15"/>
-      <c r="B3" s="15"/>
+      <c r="A3" s="24"/>
+      <c r="B3" s="24"/>
       <c r="C3" s="9" t="s">
-        <v>185</v>
+        <v>170</v>
       </c>
       <c r="D3" s="9">
         <v>1.5</v>
@@ -5307,10 +6502,10 @@
       </c>
     </row>
     <row r="4" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A4" s="15"/>
-      <c r="B4" s="15"/>
+      <c r="A4" s="24"/>
+      <c r="B4" s="24"/>
       <c r="C4" s="9" t="s">
-        <v>186</v>
+        <v>171</v>
       </c>
       <c r="D4" s="9">
         <v>2.5</v>
@@ -5323,10 +6518,10 @@
       </c>
     </row>
     <row r="5" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A5" s="15"/>
-      <c r="B5" s="15"/>
+      <c r="A5" s="24"/>
+      <c r="B5" s="24"/>
       <c r="C5" s="9" t="s">
-        <v>187</v>
+        <v>172</v>
       </c>
       <c r="D5" s="9">
         <v>2.5</v>
